--- a/output/spreadsheet/Основная таблица ИБ12 (ВК).xlsx
+++ b/output/spreadsheet/Основная таблица ИБ12 (ВК).xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -234,6 +234,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -699,10 +720,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +7.650, 3 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G2" s="27" t="n">
+      <c r="G2" s="34" t="n">
         <v>45477</v>
       </c>
-      <c r="H2" s="27" t="n">
+      <c r="H2" s="34" t="n">
         <v>45479</v>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -743,10 +764,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +10.650, 4 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G3" s="27" t="n">
+      <c r="G3" s="34" t="n">
         <v>45480</v>
       </c>
-      <c r="H3" s="27" t="n">
+      <c r="H3" s="34" t="n">
         <v>45481</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -787,10 +808,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +13.650, 5 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G4" s="27" t="n">
+      <c r="G4" s="34" t="n">
         <v>45482</v>
       </c>
-      <c r="H4" s="27" t="n">
+      <c r="H4" s="34" t="n">
         <v>45483</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -831,10 +852,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +16.650, 6 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="34" t="n">
         <v>45484</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="34" t="n">
         <v>45488</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -875,10 +896,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +19.650, 7 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="34" t="n">
         <v>45489</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="34" t="n">
         <v>45492</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -919,10 +940,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +22.650, 8 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="34" t="n">
         <v>45518</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="34" t="n">
         <v>45522</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -963,10 +984,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +25.650, 9 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="34" t="n">
         <v>45527</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="34" t="n">
         <v>45531</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1007,10 +1028,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +28.650, 10 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="34" t="n">
         <v>45539</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="34" t="n">
         <v>45543</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1051,10 +1072,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +31.650, 11 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="34" t="n">
         <v>45544</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="34" t="n">
         <v>45548</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1095,10 +1116,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +34.650, 12 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="34" t="n">
         <v>45549</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="34" t="n">
         <v>45553</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1139,10 +1160,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +37.650, 13 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="34" t="n">
         <v>45554</v>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="34" t="n">
         <v>45587</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1183,10 +1204,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +40.650, 14 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="34" t="n">
         <v>45558</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="34" t="n">
         <v>45561</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1227,10 +1248,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +43.650, 15 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="34" t="n">
         <v>45562</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="34" t="n">
         <v>45565</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1271,10 +1292,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +46.650, 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="34" t="n">
         <v>45566</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="34" t="n">
         <v>45569</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1315,10 +1336,10 @@
           <t>Монтаж полипропиленовых трубопроводов, гильз для стояков и горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.1,Т3.1,Т4.1 с отм. -0.780 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="34" t="n">
         <v>45570</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="34" t="n">
         <v>45573</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1359,10 +1380,10 @@
           <t>Монтаж этажных распределительных коллекторов систем В1.1, Т3.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 9с-10с/Вс-Гс</t>
         </is>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="34" t="n">
         <v>45673</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="34" t="n">
         <v>45698</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1403,10 +1424,10 @@
           <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.1, Т3.1 с отм. +0.140 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="G18" s="34" t="n">
         <v>45960</v>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="34" t="n">
         <v>45962</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1447,10 +1468,10 @@
           <t>Монтаж водомерных узлов сетей В1.1, Т3.1 на отм. +0.140, 1 этаж в/о 2с-6с/Бс-Дс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G19" s="27" t="n">
+      <c r="G19" s="34" t="n">
         <v>45807</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="34" t="n">
         <v>45841</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1491,10 +1512,10 @@
           <t>Монтаж гибких подводок и смесителей систем В1.1, Т3.1 с отм. +0.140 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="34" t="n">
         <v>45974</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="34" t="n">
         <v>45974</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1535,10 +1556,10 @@
           <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G21" s="34" t="n">
         <v>45954</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="34" t="n">
         <v>45969</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1579,10 +1600,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов систем В1.1,Т3.1,Т4.1 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="G22" s="34" t="n">
         <v>45954</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="34" t="n">
         <v>45969</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1619,8 +1640,8 @@
         </is>
       </c>
       <c r="F23" s="7" t="n"/>
-      <c r="G23" s="28" t="n"/>
-      <c r="H23" s="28" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="35" t="n"/>
       <c r="I23" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -1659,10 +1680,10 @@
           <t>Изоляция полипропиленовых трубопроводов систем В1.1,Т3.1,Т4.1 с отм. -0.780 до отм. +48.150, с подвала по 16 этаж в/о 2с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="34" t="n">
         <v>45699</v>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H24" s="34" t="n">
         <v>45702</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1703,10 +1724,10 @@
           <t>Проведение промывки трубопроводов системы ХВС (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G25" s="27" t="n">
+      <c r="G25" s="34" t="n">
         <v>45703</v>
       </c>
-      <c r="H25" s="27" t="n">
+      <c r="H25" s="34" t="n">
         <v>45707</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1743,8 +1764,8 @@
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
-      <c r="G26" s="29" t="n"/>
-      <c r="H26" s="29" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
       <c r="I26" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1779,8 +1800,8 @@
         </is>
       </c>
       <c r="F27" s="9" t="n"/>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="29" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
       <c r="I27" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1815,8 +1836,8 @@
         </is>
       </c>
       <c r="F28" s="9" t="n"/>
-      <c r="G28" s="29" t="n"/>
-      <c r="H28" s="29" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="36" t="n"/>
       <c r="I28" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1851,8 +1872,8 @@
         </is>
       </c>
       <c r="F29" s="9" t="n"/>
-      <c r="G29" s="29" t="n"/>
-      <c r="H29" s="29" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="H29" s="36" t="n"/>
       <c r="I29" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1887,8 +1908,8 @@
         </is>
       </c>
       <c r="F30" s="9" t="n"/>
-      <c r="G30" s="29" t="n"/>
-      <c r="H30" s="29" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
       <c r="I30" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1931,10 +1952,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +52.650, 18 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G31" s="27" t="n">
+      <c r="G31" s="34" t="n">
         <v>45576</v>
       </c>
-      <c r="H31" s="27" t="n">
+      <c r="H31" s="34" t="n">
         <v>45578</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1975,10 +1996,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +55.650, 19 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G32" s="27" t="n">
+      <c r="G32" s="34" t="n">
         <v>45579</v>
       </c>
-      <c r="H32" s="27" t="n">
+      <c r="H32" s="34" t="n">
         <v>45580</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2019,10 +2040,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +58.650, 20 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G33" s="27" t="n">
+      <c r="G33" s="34" t="n">
         <v>45581</v>
       </c>
-      <c r="H33" s="27" t="n">
+      <c r="H33" s="34" t="n">
         <v>45582</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2063,10 +2084,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +61.650, 21 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G34" s="27" t="n">
+      <c r="G34" s="34" t="n">
         <v>45583</v>
       </c>
-      <c r="H34" s="27" t="n">
+      <c r="H34" s="34" t="n">
         <v>45585</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2107,10 +2128,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +64.650, 22 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G35" s="27" t="n">
+      <c r="G35" s="34" t="n">
         <v>45586</v>
       </c>
-      <c r="H35" s="27" t="n">
+      <c r="H35" s="34" t="n">
         <v>45587</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2151,10 +2172,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +67.650, 23 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G36" s="27" t="n">
+      <c r="G36" s="34" t="n">
         <v>45588</v>
       </c>
-      <c r="H36" s="27" t="n">
+      <c r="H36" s="34" t="n">
         <v>45590</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2195,10 +2216,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +70.650, 24 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G37" s="27" t="n">
+      <c r="G37" s="34" t="n">
         <v>45634</v>
       </c>
-      <c r="H37" s="27" t="n">
+      <c r="H37" s="34" t="n">
         <v>45635</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2239,10 +2260,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +73.650, 25 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="G38" s="34" t="n">
         <v>45635</v>
       </c>
-      <c r="H38" s="27" t="n">
+      <c r="H38" s="34" t="n">
         <v>45636</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2283,10 +2304,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +76.650, 26 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G39" s="27" t="n">
+      <c r="G39" s="34" t="n">
         <v>45637</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H39" s="34" t="n">
         <v>45639</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2327,10 +2348,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +79.650, 27 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G40" s="27" t="n">
+      <c r="G40" s="34" t="n">
         <v>45639</v>
       </c>
-      <c r="H40" s="27" t="n">
+      <c r="H40" s="34" t="n">
         <v>45641</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2371,10 +2392,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +82.650, 28 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G41" s="27" t="n">
+      <c r="G41" s="34" t="n">
         <v>45642</v>
       </c>
-      <c r="H41" s="27" t="n">
+      <c r="H41" s="34" t="n">
         <v>45644</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2415,10 +2436,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +85.650, 29 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G42" s="27" t="n">
+      <c r="G42" s="34" t="n">
         <v>45645</v>
       </c>
-      <c r="H42" s="27" t="n">
+      <c r="H42" s="34" t="n">
         <v>45648</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2459,10 +2480,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +88.650, 30 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G43" s="27" t="n">
+      <c r="G43" s="34" t="n">
         <v>45649</v>
       </c>
-      <c r="H43" s="27" t="n">
+      <c r="H43" s="34" t="n">
         <v>45652</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2503,10 +2524,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +91.650, 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G44" s="27" t="n">
+      <c r="G44" s="34" t="n">
         <v>45684</v>
       </c>
-      <c r="H44" s="27" t="n">
+      <c r="H44" s="34" t="n">
         <v>45686</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2547,10 +2568,10 @@
           <t>Монтаж полипропиленовых трубопроводов, гильз для стояков и горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.2,Т3.2,Т4.2 с отм. -0.780 до отм. +93.150, с подвала по 31 этаж в/о 9с-11с/Вс-Дс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G45" s="27" t="n">
+      <c r="G45" s="34" t="n">
         <v>45687</v>
       </c>
-      <c r="H45" s="27" t="n">
+      <c r="H45" s="34" t="n">
         <v>45689</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2591,10 +2612,10 @@
           <t>Монтаж этажных распределительных коллекторов систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 9с-10с/Вс-Гс(Секция №12.1)</t>
         </is>
       </c>
-      <c r="G46" s="27" t="n">
+      <c r="G46" s="34" t="n">
         <v>45673</v>
       </c>
-      <c r="H46" s="27" t="n">
+      <c r="H46" s="34" t="n">
         <v>45952</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2635,10 +2656,10 @@
           <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G47" s="27" t="n">
+      <c r="G47" s="34" t="n">
         <v>45963</v>
       </c>
-      <c r="H47" s="27" t="n">
+      <c r="H47" s="34" t="n">
         <v>45965</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2679,10 +2700,10 @@
           <t>Монтаж гибких подводок и смесителей систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G48" s="27" t="n">
+      <c r="G48" s="34" t="n">
         <v>45842</v>
       </c>
-      <c r="H48" s="27" t="n">
+      <c r="H48" s="34" t="n">
         <v>45901</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2723,10 +2744,10 @@
           <t>Монтаж устройства внутриквартирного пожаротушения систем В1.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес ( (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G49" s="27" t="n">
+      <c r="G49" s="34" t="n">
         <v>45970</v>
       </c>
-      <c r="H49" s="27" t="n">
+      <c r="H49" s="34" t="n">
         <v>45982</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2767,10 +2788,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов систем В1.2,Т3.2,Т4.2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G50" s="27" t="n">
+      <c r="G50" s="34" t="n">
         <v>45970</v>
       </c>
-      <c r="H50" s="27" t="n">
+      <c r="H50" s="34" t="n">
         <v>45982</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2807,8 +2828,8 @@
         </is>
       </c>
       <c r="F51" s="7" t="n"/>
-      <c r="G51" s="28" t="n"/>
-      <c r="H51" s="28" t="n"/>
+      <c r="G51" s="35" t="n"/>
+      <c r="H51" s="35" t="n"/>
       <c r="I51" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -2847,10 +2868,10 @@
           <t>Изоляция полипропиленовых трубопроводов с отм. -0.780 до отм. +93.150, с подвала по 31 этаж в/о 9с-11с/Вс-Дс систем В1.2,Т3.2,Т4.2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G52" s="27" t="n">
+      <c r="G52" s="34" t="n">
         <v>45953</v>
       </c>
-      <c r="H52" s="27" t="n">
+      <c r="H52" s="34" t="n">
         <v>45956</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2891,10 +2912,10 @@
           <t>Проведение промывки трубопроводов системы ХВС (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G53" s="27" t="n">
+      <c r="G53" s="34" t="n">
         <v>45957</v>
       </c>
-      <c r="H53" s="27" t="n">
+      <c r="H53" s="34" t="n">
         <v>45961</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2931,8 +2952,8 @@
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
-      <c r="G54" s="29" t="n"/>
-      <c r="H54" s="29" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
       <c r="I54" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -2967,8 +2988,8 @@
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
-      <c r="G55" s="29" t="n"/>
-      <c r="H55" s="29" t="n"/>
+      <c r="G55" s="36" t="n"/>
+      <c r="H55" s="36" t="n"/>
       <c r="I55" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3003,8 +3024,8 @@
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
-      <c r="G56" s="29" t="n"/>
-      <c r="H56" s="29" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="36" t="n"/>
       <c r="I56" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3039,8 +3060,8 @@
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
-      <c r="G57" s="29" t="n"/>
-      <c r="H57" s="29" t="n"/>
+      <c r="G57" s="36" t="n"/>
+      <c r="H57" s="36" t="n"/>
       <c r="I57" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3075,8 +3096,8 @@
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
-      <c r="G58" s="29" t="n"/>
-      <c r="H58" s="29" t="n"/>
+      <c r="G58" s="36" t="n"/>
+      <c r="H58" s="36" t="n"/>
       <c r="I58" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3120,10 +3141,10 @@
           <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G59" s="27" t="n">
+      <c r="G59" s="34" t="n">
         <v>45513</v>
       </c>
-      <c r="H59" s="27" t="n">
+      <c r="H59" s="34" t="n">
         <v>45748</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3164,10 +3185,10 @@
           <t>Монтаж сантехнического оборудования системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G60" s="27" t="n">
+      <c r="G60" s="34" t="n">
         <v>45847</v>
       </c>
-      <c r="H60" s="27" t="n">
+      <c r="H60" s="34" t="n">
         <v>45910</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3208,10 +3229,10 @@
           <t>Проведение испытания систем канализации и водостоков системы бытовой канализации К1 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G61" s="27" t="n">
+      <c r="G61" s="34" t="n">
         <v>45954</v>
       </c>
-      <c r="H61" s="27" t="n">
+      <c r="H61" s="34" t="n">
         <v>45969</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3248,8 +3269,8 @@
         </is>
       </c>
       <c r="F62" s="11" t="n"/>
-      <c r="G62" s="30" t="n"/>
-      <c r="H62" s="30" t="n"/>
+      <c r="G62" s="37" t="n"/>
+      <c r="H62" s="37" t="n"/>
       <c r="I62" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3284,8 +3305,8 @@
         </is>
       </c>
       <c r="F63" s="9" t="n"/>
-      <c r="G63" s="29" t="n"/>
-      <c r="H63" s="29" t="n"/>
+      <c r="G63" s="36" t="n"/>
+      <c r="H63" s="36" t="n"/>
       <c r="I63" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3328,10 +3349,10 @@
           <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации встроенных помещений К1.1 на отм. +0.140, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G64" s="27" t="n">
+      <c r="G64" s="34" t="n">
         <v>45982</v>
       </c>
-      <c r="H64" s="27" t="n">
+      <c r="H64" s="34" t="n">
         <v>45983</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3376,10 +3397,10 @@
           <t>Монтаж сантехнического оборудования системы бытовой канализации встроенных помещений К1.1 на отм. +0.140, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G65" s="27" t="n">
+      <c r="G65" s="34" t="n">
         <v>45984</v>
       </c>
-      <c r="H65" s="27" t="n">
+      <c r="H65" s="34" t="n">
         <v>45984</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3424,10 +3445,10 @@
           <t>Проведение испытания систем канализации и водостоков системы бытовой канализации встроенных помещений К1.1 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G66" s="27" t="n">
+      <c r="G66" s="34" t="n">
         <v>45985</v>
       </c>
-      <c r="H66" s="27" t="n">
+      <c r="H66" s="34" t="n">
         <v>45985</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3468,8 +3489,8 @@
         </is>
       </c>
       <c r="F67" s="11" t="n"/>
-      <c r="G67" s="30" t="n"/>
-      <c r="H67" s="30" t="n"/>
+      <c r="G67" s="37" t="n"/>
+      <c r="H67" s="37" t="n"/>
       <c r="I67" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3504,8 +3525,8 @@
         </is>
       </c>
       <c r="F68" s="9" t="n"/>
-      <c r="G68" s="29" t="n"/>
-      <c r="H68" s="29" t="n"/>
+      <c r="G68" s="36" t="n"/>
+      <c r="H68" s="36" t="n"/>
       <c r="I68" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3549,10 +3570,10 @@
           <t>Проведение испытания систем канализации и водостоков системы внутреннего водостока К2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G69" s="27" t="n">
+      <c r="G69" s="34" t="n">
         <v>45520</v>
       </c>
-      <c r="H69" s="27" t="n">
+      <c r="H69" s="34" t="n">
         <v>45953</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3594,8 +3615,8 @@
         </is>
       </c>
       <c r="F70" s="11" t="n"/>
-      <c r="G70" s="30" t="n"/>
-      <c r="H70" s="30" t="n"/>
+      <c r="G70" s="37" t="n"/>
+      <c r="H70" s="37" t="n"/>
       <c r="I70" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3634,10 +3655,10 @@
           <t>Освидетельствование участков сетей инженерно-технического обеспечения системы внутреннего водостока К2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G71" s="27" t="n">
+      <c r="G71" s="34" t="n">
         <v>45954</v>
       </c>
-      <c r="H71" s="27" t="n">
+      <c r="H71" s="34" t="n">
         <v>45956</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3674,8 +3695,8 @@
         </is>
       </c>
       <c r="F72" s="9" t="n"/>
-      <c r="G72" s="29" t="n"/>
-      <c r="H72" s="29" t="n"/>
+      <c r="G72" s="36" t="n"/>
+      <c r="H72" s="36" t="n"/>
       <c r="I72" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3718,10 +3739,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы напорной дренажной канализации К13, К13н (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G73" s="27" t="n">
+      <c r="G73" s="34" t="n">
         <v>45523</v>
       </c>
-      <c r="H73" s="27" t="n">
+      <c r="H73" s="34" t="n">
         <v>45953</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3758,8 +3779,8 @@
         </is>
       </c>
       <c r="F74" s="7" t="n"/>
-      <c r="G74" s="28" t="n"/>
-      <c r="H74" s="28" t="n"/>
+      <c r="G74" s="35" t="n"/>
+      <c r="H74" s="35" t="n"/>
       <c r="I74" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -3798,10 +3819,10 @@
           <t>Проведение испытания систем канализации и водостоков системы напорной дренажной канализации К13, К13н (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G75" s="27" t="n">
+      <c r="G75" s="34" t="n">
         <v>45954</v>
       </c>
-      <c r="H75" s="27" t="n">
+      <c r="H75" s="34" t="n">
         <v>45954</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3838,8 +3859,8 @@
         </is>
       </c>
       <c r="F76" s="11" t="n"/>
-      <c r="G76" s="30" t="n"/>
-      <c r="H76" s="30" t="n"/>
+      <c r="G76" s="37" t="n"/>
+      <c r="H76" s="37" t="n"/>
       <c r="I76" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3874,8 +3895,8 @@
         </is>
       </c>
       <c r="F77" s="13" t="n"/>
-      <c r="G77" s="31" t="n"/>
-      <c r="H77" s="31" t="n"/>
+      <c r="G77" s="38" t="n"/>
+      <c r="H77" s="38" t="n"/>
       <c r="I77" s="12" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3910,8 +3931,8 @@
         </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="29" t="n"/>
-      <c r="H78" s="29" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
       <c r="I78" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3954,10 +3975,10 @@
           <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.1 с отм. -3.350 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Ас-Жс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G79" s="27" t="n">
+      <c r="G79" s="34" t="n">
         <v>45478</v>
       </c>
-      <c r="H79" s="27" t="n">
+      <c r="H79" s="34" t="n">
         <v>45917</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -3998,10 +4019,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы противопожарного водопровода В2.1 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G80" s="27" t="n">
+      <c r="G80" s="34" t="n">
         <v>45478</v>
       </c>
-      <c r="H80" s="27" t="n">
+      <c r="H80" s="34" t="n">
         <v>45917</v>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4038,8 +4059,8 @@
         </is>
       </c>
       <c r="F81" s="7" t="n"/>
-      <c r="G81" s="28" t="n"/>
-      <c r="H81" s="28" t="n"/>
+      <c r="G81" s="35" t="n"/>
+      <c r="H81" s="35" t="n"/>
       <c r="I81" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -4078,10 +4099,10 @@
           <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов системы противопожарного водопровода В2.1 с отм. -0.970 до отм. +46.650, с подвала по 16 этаж в/о 1с-11с/Ас-Жс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G82" s="27" t="n">
+      <c r="G82" s="34" t="n">
         <v>45918</v>
       </c>
-      <c r="H82" s="27" t="n">
+      <c r="H82" s="34" t="n">
         <v>45919</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4127,10 +4148,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G83" s="27" t="n">
+      <c r="G83" s="34" t="n">
         <v>45920</v>
       </c>
-      <c r="H83" s="27" t="n">
+      <c r="H83" s="34" t="n">
         <v>45921</v>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4167,8 +4188,8 @@
         </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="29" t="n"/>
-      <c r="H84" s="29" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
       <c r="I84" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4203,8 +4224,8 @@
         </is>
       </c>
       <c r="F85" s="15" t="n"/>
-      <c r="G85" s="32" t="n"/>
-      <c r="H85" s="32" t="n"/>
+      <c r="G85" s="39" t="n"/>
+      <c r="H85" s="39" t="n"/>
       <c r="I85" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4239,8 +4260,8 @@
         </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="29" t="n"/>
-      <c r="H86" s="29" t="n"/>
+      <c r="G86" s="36" t="n"/>
+      <c r="H86" s="36" t="n"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4283,10 +4304,10 @@
           <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.2 с отм. +49.650 до отм. +94.930, с 17 этажа по тех. чердак в/о 3с-10с/Ас-Дс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G87" s="27" t="n">
+      <c r="G87" s="34" t="n">
         <v>45478</v>
       </c>
-      <c r="H87" s="27" t="n">
+      <c r="H87" s="34" t="n">
         <v>45876</v>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4327,10 +4348,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы противопожарного водопровода В2.2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G88" s="27" t="n">
+      <c r="G88" s="34" t="n">
         <v>45478</v>
       </c>
-      <c r="H88" s="27" t="n">
+      <c r="H88" s="34" t="n">
         <v>45876</v>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -4367,8 +4388,8 @@
         </is>
       </c>
       <c r="F89" s="7" t="n"/>
-      <c r="G89" s="28" t="n"/>
-      <c r="H89" s="28" t="n"/>
+      <c r="G89" s="35" t="n"/>
+      <c r="H89" s="35" t="n"/>
       <c r="I89" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -4407,10 +4428,10 @@
           <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов систем противопожарного водопровода В2.2 с отм. -0.890 до отм. +96.978, с подвала по тех. чердак в/о 3с-10с/Бс-Дс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G90" s="27" t="n">
+      <c r="G90" s="34" t="n">
         <v>45877</v>
       </c>
-      <c r="H90" s="27" t="n">
+      <c r="H90" s="34" t="n">
         <v>45878</v>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -4456,10 +4477,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G91" s="27" t="n">
+      <c r="G91" s="34" t="n">
         <v>45879</v>
       </c>
-      <c r="H91" s="27" t="n">
+      <c r="H91" s="34" t="n">
         <v>45880</v>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4496,8 +4517,8 @@
         </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="29" t="n"/>
-      <c r="H92" s="29" t="n"/>
+      <c r="G92" s="36" t="n"/>
+      <c r="H92" s="36" t="n"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4532,8 +4553,8 @@
         </is>
       </c>
       <c r="F93" s="15" t="n"/>
-      <c r="G93" s="32" t="n"/>
-      <c r="H93" s="32" t="n"/>
+      <c r="G93" s="39" t="n"/>
+      <c r="H93" s="39" t="n"/>
       <c r="I93" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4568,8 +4589,8 @@
         </is>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="G94" s="29" t="n"/>
-      <c r="H94" s="29" t="n"/>
+      <c r="G94" s="36" t="n"/>
+      <c r="H94" s="36" t="n"/>
       <c r="I94" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4612,10 +4633,10 @@
           <t>Монтаж пожарного оборудования системы автоматического пожаротушения кладовых В2 с отм. -0.548 до отм. -0.289, подвал в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G95" s="27" t="n">
+      <c r="G95" s="34" t="n">
         <v>45982</v>
       </c>
-      <c r="H95" s="27" t="n">
+      <c r="H95" s="34" t="n">
         <v>45984</v>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -4656,10 +4677,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы автоматического пожаротушения кладовых В2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G96" s="27" t="n">
+      <c r="G96" s="34" t="n">
         <v>45988</v>
       </c>
-      <c r="H96" s="27" t="n">
+      <c r="H96" s="34" t="n">
         <v>45988</v>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -4696,8 +4717,8 @@
         </is>
       </c>
       <c r="F97" s="7" t="n"/>
-      <c r="G97" s="28" t="n"/>
-      <c r="H97" s="28" t="n"/>
+      <c r="G97" s="35" t="n"/>
+      <c r="H97" s="35" t="n"/>
       <c r="I97" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -4736,10 +4757,10 @@
           <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции системы автоматического пожаротушения кладовых В2 с отм. -0.862 до отм. -0.422, подвал в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G98" s="27" t="n">
+      <c r="G98" s="34" t="n">
         <v>45996</v>
       </c>
-      <c r="H98" s="27" t="n">
+      <c r="H98" s="34" t="n">
         <v>45996</v>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -4784,10 +4805,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G99" s="27" t="n">
+      <c r="G99" s="34" t="n">
         <v>45999</v>
       </c>
-      <c r="H99" s="27" t="n">
+      <c r="H99" s="34" t="n">
         <v>45999</v>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -4824,8 +4845,8 @@
         </is>
       </c>
       <c r="F100" s="9" t="n"/>
-      <c r="G100" s="29" t="n"/>
-      <c r="H100" s="29" t="n"/>
+      <c r="G100" s="36" t="n"/>
+      <c r="H100" s="36" t="n"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4860,8 +4881,8 @@
         </is>
       </c>
       <c r="F101" s="17" t="n"/>
-      <c r="G101" s="33" t="n"/>
-      <c r="H101" s="33" t="n"/>
+      <c r="G101" s="40" t="n"/>
+      <c r="H101" s="40" t="n"/>
       <c r="I101" s="16" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4900,8 +4921,8 @@
         </is>
       </c>
       <c r="F102" s="15" t="n"/>
-      <c r="G102" s="32" t="n"/>
-      <c r="H102" s="32" t="n"/>
+      <c r="G102" s="39" t="n"/>
+      <c r="H102" s="39" t="n"/>
       <c r="I102" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4936,8 +4957,8 @@
         </is>
       </c>
       <c r="F103" s="9" t="n"/>
-      <c r="G103" s="29" t="n"/>
-      <c r="H103" s="29" t="n"/>
+      <c r="G103" s="36" t="n"/>
+      <c r="H103" s="36" t="n"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4980,10 +5001,10 @@
           <t>Монтаж основного водомерного узла системы В1 с отм. -2.580 до отм. -2.253, подвал в/о 1с-2с/Ес-Жс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G104" s="27" t="n">
+      <c r="G104" s="34" t="n">
         <v>45964</v>
       </c>
-      <c r="H104" s="27" t="n">
+      <c r="H104" s="34" t="n">
         <v>45964</v>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -5024,10 +5045,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +4.650, 2 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G105" s="27" t="n">
+      <c r="G105" s="34" t="n">
         <v>45964</v>
       </c>
-      <c r="H105" s="27" t="n">
+      <c r="H105" s="34" t="n">
         <v>45964</v>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -5068,10 +5089,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +7.650, 3 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G106" s="27" t="n">
+      <c r="G106" s="34" t="n">
         <v>45524</v>
       </c>
-      <c r="H106" s="27" t="n">
+      <c r="H106" s="34" t="n">
         <v>45527</v>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -5116,10 +5137,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +10.650, 4 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G107" s="27" t="n">
+      <c r="G107" s="34" t="n">
         <v>45524</v>
       </c>
-      <c r="H107" s="27" t="n">
+      <c r="H107" s="34" t="n">
         <v>45527</v>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5160,10 +5181,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +13.650, 5 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G108" s="27" t="n">
+      <c r="G108" s="34" t="n">
         <v>45538</v>
       </c>
-      <c r="H108" s="27" t="n">
+      <c r="H108" s="34" t="n">
         <v>45541</v>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -5204,10 +5225,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +16.650, 6 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G109" s="27" t="n">
+      <c r="G109" s="34" t="n">
         <v>45542</v>
       </c>
-      <c r="H109" s="27" t="n">
+      <c r="H109" s="34" t="n">
         <v>45545</v>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -5248,10 +5269,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +19.650, 7 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G110" s="27" t="n">
+      <c r="G110" s="34" t="n">
         <v>45546</v>
       </c>
-      <c r="H110" s="27" t="n">
+      <c r="H110" s="34" t="n">
         <v>45549</v>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -5292,10 +5313,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +22.650, 8 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G111" s="27" t="n">
+      <c r="G111" s="34" t="n">
         <v>45550</v>
       </c>
-      <c r="H111" s="27" t="n">
+      <c r="H111" s="34" t="n">
         <v>45553</v>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -5336,10 +5357,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +25.650, 9 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G112" s="27" t="n">
+      <c r="G112" s="34" t="n">
         <v>45554</v>
       </c>
-      <c r="H112" s="27" t="n">
+      <c r="H112" s="34" t="n">
         <v>45557</v>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -5380,10 +5401,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +28.650, 10 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G113" s="27" t="n">
+      <c r="G113" s="34" t="n">
         <v>45567</v>
       </c>
-      <c r="H113" s="27" t="n">
+      <c r="H113" s="34" t="n">
         <v>45570</v>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -5424,10 +5445,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +31.650, 11 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G114" s="27" t="n">
+      <c r="G114" s="34" t="n">
         <v>45571</v>
       </c>
-      <c r="H114" s="27" t="n">
+      <c r="H114" s="34" t="n">
         <v>45574</v>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -5468,10 +5489,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +34.650, 12 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G115" s="27" t="n">
+      <c r="G115" s="34" t="n">
         <v>45575</v>
       </c>
-      <c r="H115" s="27" t="n">
+      <c r="H115" s="34" t="n">
         <v>45577</v>
       </c>
       <c r="I115" s="4" t="inlineStr">
@@ -5512,10 +5533,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +37.650, 13 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G116" s="27" t="n">
+      <c r="G116" s="34" t="n">
         <v>45578</v>
       </c>
-      <c r="H116" s="27" t="n">
+      <c r="H116" s="34" t="n">
         <v>45580</v>
       </c>
       <c r="I116" s="4" t="inlineStr">
@@ -5556,10 +5577,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +40.650, 14 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G117" s="27" t="n">
+      <c r="G117" s="34" t="n">
         <v>45603</v>
       </c>
-      <c r="H117" s="27" t="n">
+      <c r="H117" s="34" t="n">
         <v>45606</v>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -5600,10 +5621,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +43.650, 15 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G118" s="27" t="n">
+      <c r="G118" s="34" t="n">
         <v>45607</v>
       </c>
-      <c r="H118" s="27" t="n">
+      <c r="H118" s="34" t="n">
         <v>45610</v>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -5644,10 +5665,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +46.650, 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G119" s="27" t="n">
+      <c r="G119" s="34" t="n">
         <v>45611</v>
       </c>
-      <c r="H119" s="27" t="n">
+      <c r="H119" s="34" t="n">
         <v>45614</v>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -5688,10 +5709,10 @@
           <t>Монтаж гильз для стояков, полипропиленовых и стальных трубопроводов, неподвижных опор и запорной арматуры систем В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной с отм. -1.250 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G120" s="27" t="n">
+      <c r="G120" s="34" t="n">
         <v>45634</v>
       </c>
-      <c r="H120" s="27" t="n">
+      <c r="H120" s="34" t="n">
         <v>45637</v>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -5732,10 +5753,10 @@
           <t>Монтаж этажных распределительных коллекторов систем В1.1, Т3.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G121" s="27" t="n">
+      <c r="G121" s="34" t="n">
         <v>45677</v>
       </c>
-      <c r="H121" s="27" t="n">
+      <c r="H121" s="34" t="n">
         <v>45865</v>
       </c>
       <c r="I121" s="4" t="inlineStr">
@@ -5776,10 +5797,10 @@
           <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.1, Т3.1 с отм. -0.210 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G122" s="27" t="n">
+      <c r="G122" s="34" t="n">
         <v>45979</v>
       </c>
-      <c r="H122" s="27" t="n">
+      <c r="H122" s="34" t="n">
         <v>45980</v>
       </c>
       <c r="I122" s="4" t="inlineStr">
@@ -5820,10 +5841,10 @@
           <t>Монтаж водомерных узлов сетей В1.1, Т3.1 на отм. -0.210, 1 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G123" s="27" t="n">
+      <c r="G123" s="34" t="n">
         <v>45812</v>
       </c>
-      <c r="H123" s="27" t="n">
+      <c r="H123" s="34" t="n">
         <v>45851</v>
       </c>
       <c r="I123" s="4" t="inlineStr">
@@ -5864,10 +5885,10 @@
           <t>Монтаж гибких подводок и смесителей систем В1.1, Т3.1 с отм. -0.210 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G124" s="27" t="n">
+      <c r="G124" s="34" t="n">
         <v>45974</v>
       </c>
-      <c r="H124" s="27" t="n">
+      <c r="H124" s="34" t="n">
         <v>45974</v>
       </c>
       <c r="I124" s="4" t="inlineStr">
@@ -5908,10 +5929,10 @@
           <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G125" s="27" t="n">
+      <c r="G125" s="34" t="n">
         <v>45952</v>
       </c>
-      <c r="H125" s="27" t="n">
+      <c r="H125" s="34" t="n">
         <v>45967</v>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -5952,10 +5973,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов систем В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G126" s="27" t="n">
+      <c r="G126" s="34" t="n">
         <v>45952</v>
       </c>
-      <c r="H126" s="27" t="n">
+      <c r="H126" s="34" t="n">
         <v>45967</v>
       </c>
       <c r="I126" s="4" t="inlineStr">
@@ -5992,8 +6013,8 @@
         </is>
       </c>
       <c r="F127" s="7" t="n"/>
-      <c r="G127" s="28" t="n"/>
-      <c r="H127" s="28" t="n"/>
+      <c r="G127" s="35" t="n"/>
+      <c r="H127" s="35" t="n"/>
       <c r="I127" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -6032,10 +6053,10 @@
           <t>Изоляция полипропиленовых и стальных трубопроводов систем В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной с отм. -1.250 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G128" s="27" t="n">
+      <c r="G128" s="34" t="n">
         <v>45866</v>
       </c>
-      <c r="H128" s="27" t="n">
+      <c r="H128" s="34" t="n">
         <v>45869</v>
       </c>
       <c r="I128" s="4" t="inlineStr">
@@ -6076,10 +6097,10 @@
           <t>Проведение промывки трубопроводов системы ХВС (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G129" s="27" t="n">
+      <c r="G129" s="34" t="n">
         <v>45870</v>
       </c>
-      <c r="H129" s="27" t="n">
+      <c r="H129" s="34" t="n">
         <v>45874</v>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -6116,8 +6137,8 @@
         </is>
       </c>
       <c r="F130" s="9" t="n"/>
-      <c r="G130" s="29" t="n"/>
-      <c r="H130" s="29" t="n"/>
+      <c r="G130" s="36" t="n"/>
+      <c r="H130" s="36" t="n"/>
       <c r="I130" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6152,8 +6173,8 @@
         </is>
       </c>
       <c r="F131" s="9" t="n"/>
-      <c r="G131" s="29" t="n"/>
-      <c r="H131" s="29" t="n"/>
+      <c r="G131" s="36" t="n"/>
+      <c r="H131" s="36" t="n"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6188,8 +6209,8 @@
         </is>
       </c>
       <c r="F132" s="9" t="n"/>
-      <c r="G132" s="29" t="n"/>
-      <c r="H132" s="29" t="n"/>
+      <c r="G132" s="36" t="n"/>
+      <c r="H132" s="36" t="n"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6224,8 +6245,8 @@
         </is>
       </c>
       <c r="F133" s="9" t="n"/>
-      <c r="G133" s="29" t="n"/>
-      <c r="H133" s="29" t="n"/>
+      <c r="G133" s="36" t="n"/>
+      <c r="H133" s="36" t="n"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6260,8 +6281,8 @@
         </is>
       </c>
       <c r="F134" s="9" t="n"/>
-      <c r="G134" s="29" t="n"/>
-      <c r="H134" s="29" t="n"/>
+      <c r="G134" s="36" t="n"/>
+      <c r="H134" s="36" t="n"/>
       <c r="I134" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6304,10 +6325,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +52.650, 18 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G135" s="27" t="n">
+      <c r="G135" s="34" t="n">
         <v>45643</v>
       </c>
-      <c r="H135" s="27" t="n">
+      <c r="H135" s="34" t="n">
         <v>45645</v>
       </c>
       <c r="I135" s="4" t="inlineStr">
@@ -6348,10 +6369,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +55.650, 19 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G136" s="27" t="n">
+      <c r="G136" s="34" t="n">
         <v>45646</v>
       </c>
-      <c r="H136" s="27" t="n">
+      <c r="H136" s="34" t="n">
         <v>45647</v>
       </c>
       <c r="I136" s="4" t="inlineStr">
@@ -6392,10 +6413,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +58.650, 20 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G137" s="27" t="n">
+      <c r="G137" s="34" t="n">
         <v>45648</v>
       </c>
-      <c r="H137" s="27" t="n">
+      <c r="H137" s="34" t="n">
         <v>45649</v>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -6436,10 +6457,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +61.650, 21 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G138" s="27" t="n">
+      <c r="G138" s="34" t="n">
         <v>45650</v>
       </c>
-      <c r="H138" s="27" t="n">
+      <c r="H138" s="34" t="n">
         <v>45651</v>
       </c>
       <c r="I138" s="4" t="inlineStr">
@@ -6480,10 +6501,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +64.650, 22 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G139" s="27" t="n">
+      <c r="G139" s="34" t="n">
         <v>45652</v>
       </c>
-      <c r="H139" s="27" t="n">
+      <c r="H139" s="34" t="n">
         <v>45654</v>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -6524,10 +6545,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +67.650, 23 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G140" s="27" t="n">
+      <c r="G140" s="34" t="n">
         <v>45655</v>
       </c>
-      <c r="H140" s="27" t="n">
+      <c r="H140" s="34" t="n">
         <v>45657</v>
       </c>
       <c r="I140" s="4" t="inlineStr">
@@ -6568,10 +6589,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +70.650, 24 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G141" s="27" t="n">
+      <c r="G141" s="34" t="n">
         <v>45658</v>
       </c>
-      <c r="H141" s="27" t="n">
+      <c r="H141" s="34" t="n">
         <v>45660</v>
       </c>
       <c r="I141" s="4" t="inlineStr">
@@ -6612,10 +6633,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +73.650, 25 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G142" s="27" t="n">
+      <c r="G142" s="34" t="n">
         <v>45672</v>
       </c>
-      <c r="H142" s="27" t="n">
+      <c r="H142" s="34" t="n">
         <v>45674</v>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -6656,10 +6677,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +76.650, 26 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G143" s="27" t="n">
+      <c r="G143" s="34" t="n">
         <v>45675</v>
       </c>
-      <c r="H143" s="27" t="n">
+      <c r="H143" s="34" t="n">
         <v>45677</v>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -6700,10 +6721,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +79.650, 27 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G144" s="27" t="n">
+      <c r="G144" s="34" t="n">
         <v>45678</v>
       </c>
-      <c r="H144" s="27" t="n">
+      <c r="H144" s="34" t="n">
         <v>45680</v>
       </c>
       <c r="I144" s="4" t="inlineStr">
@@ -6744,10 +6765,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +82.650, 28 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G145" s="27" t="n">
+      <c r="G145" s="34" t="n">
         <v>45681</v>
       </c>
-      <c r="H145" s="27" t="n">
+      <c r="H145" s="34" t="n">
         <v>45683</v>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -6788,10 +6809,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +85.650, 29 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G146" s="27" t="n">
+      <c r="G146" s="34" t="n">
         <v>45684</v>
       </c>
-      <c r="H146" s="27" t="n">
+      <c r="H146" s="34" t="n">
         <v>45686</v>
       </c>
       <c r="I146" s="4" t="inlineStr">
@@ -6832,10 +6853,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +88.650, 30 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G147" s="27" t="n">
+      <c r="G147" s="34" t="n">
         <v>45687</v>
       </c>
-      <c r="H147" s="27" t="n">
+      <c r="H147" s="34" t="n">
         <v>45689</v>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -6876,10 +6897,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +91.650, 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G148" s="27" t="n">
+      <c r="G148" s="34" t="n">
         <v>45690</v>
       </c>
-      <c r="H148" s="27" t="n">
+      <c r="H148" s="34" t="n">
         <v>45692</v>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -6920,10 +6941,10 @@
           <t>Монтаж полипропиленовых трубопроводов, гильз для стояков, горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.2,Т3.2,Т4.2 с отм. -0.947 до отм. +93.150, с подвала по 31 этаж в/о 1с-9с/Вс-Дс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G149" s="27" t="n">
+      <c r="G149" s="34" t="n">
         <v>45694</v>
       </c>
-      <c r="H149" s="27" t="n">
+      <c r="H149" s="34" t="n">
         <v>45696</v>
       </c>
       <c r="I149" s="4" t="inlineStr">
@@ -6964,10 +6985,10 @@
           <t>Монтаж этажных распределительных коллекторов систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G150" s="27" t="n">
+      <c r="G150" s="34" t="n">
         <v>45677</v>
       </c>
-      <c r="H150" s="27" t="n">
+      <c r="H150" s="34" t="n">
         <v>45952</v>
       </c>
       <c r="I150" s="4" t="inlineStr">
@@ -7008,10 +7029,10 @@
           <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G151" s="27" t="n">
+      <c r="G151" s="34" t="n">
         <v>45981</v>
       </c>
-      <c r="H151" s="27" t="n">
+      <c r="H151" s="34" t="n">
         <v>45983</v>
       </c>
       <c r="I151" s="4" t="inlineStr">
@@ -7052,10 +7073,10 @@
           <t>Монтаж гибких подводок и смесителей систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G152" s="27" t="n">
+      <c r="G152" s="34" t="n">
         <v>45852</v>
       </c>
-      <c r="H152" s="27" t="n">
+      <c r="H152" s="34" t="n">
         <v>45889</v>
       </c>
       <c r="I152" s="4" t="inlineStr">
@@ -7096,10 +7117,10 @@
           <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G153" s="27" t="n">
+      <c r="G153" s="34" t="n">
         <v>45968</v>
       </c>
-      <c r="H153" s="27" t="n">
+      <c r="H153" s="34" t="n">
         <v>45978</v>
       </c>
       <c r="I153" s="4" t="inlineStr">
@@ -7140,10 +7161,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов систем В1.2,Т3.2,Т4.2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G154" s="27" t="n">
+      <c r="G154" s="34" t="n">
         <v>45968</v>
       </c>
-      <c r="H154" s="27" t="n">
+      <c r="H154" s="34" t="n">
         <v>45978</v>
       </c>
       <c r="I154" s="4" t="inlineStr">
@@ -7180,8 +7201,8 @@
         </is>
       </c>
       <c r="F155" s="7" t="n"/>
-      <c r="G155" s="28" t="n"/>
-      <c r="H155" s="28" t="n"/>
+      <c r="G155" s="35" t="n"/>
+      <c r="H155" s="35" t="n"/>
       <c r="I155" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -7220,10 +7241,10 @@
           <t>Изоляция полипропиленовых трубопроводов систем В1.2,Т3.2,Т4.2 с отм. -0.947 до отм. +93.150,с подвала по 31 этаж в/о 1с-9с/Вс-Дс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G156" s="27" t="n">
+      <c r="G156" s="34" t="n">
         <v>45953</v>
       </c>
-      <c r="H156" s="27" t="n">
+      <c r="H156" s="34" t="n">
         <v>45956</v>
       </c>
       <c r="I156" s="4" t="inlineStr">
@@ -7264,10 +7285,10 @@
           <t>Проведение промывки трубопроводов системы ХВС (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G157" s="27" t="n">
+      <c r="G157" s="34" t="n">
         <v>45957</v>
       </c>
-      <c r="H157" s="27" t="n">
+      <c r="H157" s="34" t="n">
         <v>45961</v>
       </c>
       <c r="I157" s="4" t="inlineStr">
@@ -7304,8 +7325,8 @@
         </is>
       </c>
       <c r="F158" s="9" t="n"/>
-      <c r="G158" s="29" t="n"/>
-      <c r="H158" s="29" t="n"/>
+      <c r="G158" s="36" t="n"/>
+      <c r="H158" s="36" t="n"/>
       <c r="I158" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7340,8 +7361,8 @@
         </is>
       </c>
       <c r="F159" s="9" t="n"/>
-      <c r="G159" s="29" t="n"/>
-      <c r="H159" s="29" t="n"/>
+      <c r="G159" s="36" t="n"/>
+      <c r="H159" s="36" t="n"/>
       <c r="I159" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7376,8 +7397,8 @@
         </is>
       </c>
       <c r="F160" s="9" t="n"/>
-      <c r="G160" s="29" t="n"/>
-      <c r="H160" s="29" t="n"/>
+      <c r="G160" s="36" t="n"/>
+      <c r="H160" s="36" t="n"/>
       <c r="I160" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7412,8 +7433,8 @@
         </is>
       </c>
       <c r="F161" s="9" t="n"/>
-      <c r="G161" s="29" t="n"/>
-      <c r="H161" s="29" t="n"/>
+      <c r="G161" s="36" t="n"/>
+      <c r="H161" s="36" t="n"/>
       <c r="I161" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7448,8 +7469,8 @@
         </is>
       </c>
       <c r="F162" s="9" t="n"/>
-      <c r="G162" s="29" t="n"/>
-      <c r="H162" s="29" t="n"/>
+      <c r="G162" s="36" t="n"/>
+      <c r="H162" s="36" t="n"/>
       <c r="I162" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7492,10 +7513,10 @@
           <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации К1 с отм. +4.650 до отм. +91.650 в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G163" s="27" t="n">
+      <c r="G163" s="34" t="n">
         <v>45516</v>
       </c>
-      <c r="H163" s="27" t="n">
+      <c r="H163" s="34" t="n">
         <v>45748</v>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -7536,10 +7557,10 @@
           <t>Монтаж сантехнического оборудования системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G164" s="27" t="n">
+      <c r="G164" s="34" t="n">
         <v>45852</v>
       </c>
-      <c r="H164" s="27" t="n">
+      <c r="H164" s="34" t="n">
         <v>45906</v>
       </c>
       <c r="I164" s="4" t="inlineStr">
@@ -7580,10 +7601,10 @@
           <t>Проведение испытания систем канализации и водостоков системы бытовой канализации К1 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G165" s="27" t="n">
+      <c r="G165" s="34" t="n">
         <v>45952</v>
       </c>
-      <c r="H165" s="27" t="n">
+      <c r="H165" s="34" t="n">
         <v>45967</v>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -7620,8 +7641,8 @@
         </is>
       </c>
       <c r="F166" s="11" t="n"/>
-      <c r="G166" s="30" t="n"/>
-      <c r="H166" s="30" t="n"/>
+      <c r="G166" s="37" t="n"/>
+      <c r="H166" s="37" t="n"/>
       <c r="I166" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7656,8 +7677,8 @@
         </is>
       </c>
       <c r="F167" s="9" t="n"/>
-      <c r="G167" s="29" t="n"/>
-      <c r="H167" s="29" t="n"/>
+      <c r="G167" s="36" t="n"/>
+      <c r="H167" s="36" t="n"/>
       <c r="I167" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7700,10 +7721,10 @@
           <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации встроенных помещений К1.1 на отм. -0.210, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G168" s="27" t="n">
+      <c r="G168" s="34" t="n">
         <v>45985</v>
       </c>
-      <c r="H168" s="27" t="n">
+      <c r="H168" s="34" t="n">
         <v>45986</v>
       </c>
       <c r="I168" s="4" t="inlineStr">
@@ -7748,10 +7769,10 @@
           <t>Монтаж сантехнического оборудования системы бытовой канализации встроенных помещений К1.1 на отм. -0.210, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G169" s="27" t="n">
+      <c r="G169" s="34" t="n">
         <v>45987</v>
       </c>
-      <c r="H169" s="27" t="n">
+      <c r="H169" s="34" t="n">
         <v>45987</v>
       </c>
       <c r="I169" s="4" t="inlineStr">
@@ -7796,10 +7817,10 @@
           <t>Проведение испытания систем канализации и водостоков системы бытовой канализации встроенных помещений К1.1 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G170" s="27" t="n">
+      <c r="G170" s="34" t="n">
         <v>45988</v>
       </c>
-      <c r="H170" s="27" t="n">
+      <c r="H170" s="34" t="n">
         <v>45988</v>
       </c>
       <c r="I170" s="4" t="inlineStr">
@@ -7840,8 +7861,8 @@
         </is>
       </c>
       <c r="F171" s="11" t="n"/>
-      <c r="G171" s="30" t="n"/>
-      <c r="H171" s="30" t="n"/>
+      <c r="G171" s="37" t="n"/>
+      <c r="H171" s="37" t="n"/>
       <c r="I171" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7876,8 +7897,8 @@
         </is>
       </c>
       <c r="F172" s="9" t="n"/>
-      <c r="G172" s="29" t="n"/>
-      <c r="H172" s="29" t="n"/>
+      <c r="G172" s="36" t="n"/>
+      <c r="H172" s="36" t="n"/>
       <c r="I172" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7921,10 +7942,10 @@
           <t>Проведение испытания систем канализации и водостоков системы внутреннего водостока К2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G173" s="27" t="n">
+      <c r="G173" s="34" t="n">
         <v>45524</v>
       </c>
-      <c r="H173" s="27" t="n">
+      <c r="H173" s="34" t="n">
         <v>45737</v>
       </c>
       <c r="I173" s="4" t="inlineStr">
@@ -7961,8 +7982,8 @@
         </is>
       </c>
       <c r="F174" s="11" t="n"/>
-      <c r="G174" s="30" t="n"/>
-      <c r="H174" s="30" t="n"/>
+      <c r="G174" s="37" t="n"/>
+      <c r="H174" s="37" t="n"/>
       <c r="I174" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8001,10 +8022,10 @@
           <t>Освидетельствование участков сетей инженерно-технического обеспечения системы внутреннего водостока К2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G175" s="27" t="n">
+      <c r="G175" s="34" t="n">
         <v>45911</v>
       </c>
-      <c r="H175" s="27" t="n">
+      <c r="H175" s="34" t="n">
         <v>45913</v>
       </c>
       <c r="I175" s="4" t="inlineStr">
@@ -8041,8 +8062,8 @@
         </is>
       </c>
       <c r="F176" s="9" t="n"/>
-      <c r="G176" s="29" t="n"/>
-      <c r="H176" s="29" t="n"/>
+      <c r="G176" s="36" t="n"/>
+      <c r="H176" s="36" t="n"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8085,10 +8106,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы напорной дренажной канализации К13, К13н, К14н (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G177" s="27" t="n">
+      <c r="G177" s="34" t="n">
         <v>45531</v>
       </c>
-      <c r="H177" s="27" t="n">
+      <c r="H177" s="34" t="n">
         <v>45910</v>
       </c>
       <c r="I177" s="4" t="inlineStr">
@@ -8125,8 +8146,8 @@
         </is>
       </c>
       <c r="F178" s="7" t="n"/>
-      <c r="G178" s="28" t="n"/>
-      <c r="H178" s="28" t="n"/>
+      <c r="G178" s="35" t="n"/>
+      <c r="H178" s="35" t="n"/>
       <c r="I178" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -8165,10 +8186,10 @@
           <t>Проведение испытания систем канализации и водостоков системы напорной дренажной канализации К13, К13н, К14н (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G179" s="27" t="n">
+      <c r="G179" s="34" t="n">
         <v>45911</v>
       </c>
-      <c r="H179" s="27" t="n">
+      <c r="H179" s="34" t="n">
         <v>45911</v>
       </c>
       <c r="I179" s="4" t="inlineStr">
@@ -8205,8 +8226,8 @@
         </is>
       </c>
       <c r="F180" s="11" t="n"/>
-      <c r="G180" s="30" t="n"/>
-      <c r="H180" s="30" t="n"/>
+      <c r="G180" s="37" t="n"/>
+      <c r="H180" s="37" t="n"/>
       <c r="I180" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8241,8 +8262,8 @@
         </is>
       </c>
       <c r="F181" s="13" t="n"/>
-      <c r="G181" s="31" t="n"/>
-      <c r="H181" s="31" t="n"/>
+      <c r="G181" s="38" t="n"/>
+      <c r="H181" s="38" t="n"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8277,8 +8298,8 @@
         </is>
       </c>
       <c r="F182" s="9" t="n"/>
-      <c r="G182" s="29" t="n"/>
-      <c r="H182" s="29" t="n"/>
+      <c r="G182" s="36" t="n"/>
+      <c r="H182" s="36" t="n"/>
       <c r="I182" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8322,10 +8343,10 @@
           <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.1 с отм. -3.350 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G183" s="27" t="n">
+      <c r="G183" s="34" t="n">
         <v>45526</v>
       </c>
-      <c r="H183" s="27" t="n">
+      <c r="H183" s="34" t="n">
         <v>45917</v>
       </c>
       <c r="I183" s="4" t="inlineStr">
@@ -8366,10 +8387,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы противопожарного водопровода В2.1 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G184" s="27" t="n">
+      <c r="G184" s="34" t="n">
         <v>45526</v>
       </c>
-      <c r="H184" s="27" t="n">
+      <c r="H184" s="34" t="n">
         <v>45917</v>
       </c>
       <c r="I184" s="4" t="inlineStr">
@@ -8406,8 +8427,8 @@
         </is>
       </c>
       <c r="F185" s="7" t="n"/>
-      <c r="G185" s="28" t="n"/>
-      <c r="H185" s="28" t="n"/>
+      <c r="G185" s="35" t="n"/>
+      <c r="H185" s="35" t="n"/>
       <c r="I185" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -8446,10 +8467,10 @@
           <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции систем противопожарного водопровода В2.1 с отм. -2.050 до отм. +46.650, с подвала по 16 этаж в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G186" s="27" t="n">
+      <c r="G186" s="34" t="n">
         <v>45918</v>
       </c>
-      <c r="H186" s="27" t="n">
+      <c r="H186" s="34" t="n">
         <v>45919</v>
       </c>
       <c r="I186" s="4" t="inlineStr">
@@ -8494,10 +8515,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G187" s="27" t="n">
+      <c r="G187" s="34" t="n">
         <v>45920</v>
       </c>
-      <c r="H187" s="27" t="n">
+      <c r="H187" s="34" t="n">
         <v>45921</v>
       </c>
       <c r="I187" s="4" t="inlineStr">
@@ -8534,8 +8555,8 @@
         </is>
       </c>
       <c r="F188" s="9" t="n"/>
-      <c r="G188" s="29" t="n"/>
-      <c r="H188" s="29" t="n"/>
+      <c r="G188" s="36" t="n"/>
+      <c r="H188" s="36" t="n"/>
       <c r="I188" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8570,8 +8591,8 @@
         </is>
       </c>
       <c r="F189" s="15" t="n"/>
-      <c r="G189" s="32" t="n"/>
-      <c r="H189" s="32" t="n"/>
+      <c r="G189" s="39" t="n"/>
+      <c r="H189" s="39" t="n"/>
       <c r="I189" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8606,8 +8627,8 @@
         </is>
       </c>
       <c r="F190" s="9" t="n"/>
-      <c r="G190" s="29" t="n"/>
-      <c r="H190" s="29" t="n"/>
+      <c r="G190" s="36" t="n"/>
+      <c r="H190" s="36" t="n"/>
       <c r="I190" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8650,10 +8671,10 @@
           <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.2 с отм. +50.950 до отм. +94.630, с 17 этажа по тех. чердак в/о 1с-9с/Бс-Дс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G191" s="27" t="n">
+      <c r="G191" s="34" t="n">
         <v>45526</v>
       </c>
-      <c r="H191" s="27" t="n">
+      <c r="H191" s="34" t="n">
         <v>45876</v>
       </c>
       <c r="I191" s="4" t="inlineStr">
@@ -8694,10 +8715,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы противопожарного водопровода В2.2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G192" s="27" t="n">
+      <c r="G192" s="34" t="n">
         <v>45526</v>
       </c>
-      <c r="H192" s="27" t="n">
+      <c r="H192" s="34" t="n">
         <v>45876</v>
       </c>
       <c r="I192" s="4" t="inlineStr">
@@ -8734,8 +8755,8 @@
         </is>
       </c>
       <c r="F193" s="7" t="n"/>
-      <c r="G193" s="28" t="n"/>
-      <c r="H193" s="28" t="n"/>
+      <c r="G193" s="35" t="n"/>
+      <c r="H193" s="35" t="n"/>
       <c r="I193" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -8774,10 +8795,10 @@
           <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции систем противопожарного водопровода В2.2 с отм. -1.071 до отм. +94.930, с подвала по тех. чердак в/о 1с-9с/Бс-Дс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G194" s="27" t="n">
+      <c r="G194" s="34" t="n">
         <v>45877</v>
       </c>
-      <c r="H194" s="27" t="n">
+      <c r="H194" s="34" t="n">
         <v>45878</v>
       </c>
       <c r="I194" s="4" t="inlineStr">
@@ -8822,10 +8843,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G195" s="27" t="n">
+      <c r="G195" s="34" t="n">
         <v>45879</v>
       </c>
-      <c r="H195" s="27" t="n">
+      <c r="H195" s="34" t="n">
         <v>45880</v>
       </c>
       <c r="I195" s="4" t="inlineStr">
@@ -8862,8 +8883,8 @@
         </is>
       </c>
       <c r="F196" s="9" t="n"/>
-      <c r="G196" s="29" t="n"/>
-      <c r="H196" s="29" t="n"/>
+      <c r="G196" s="36" t="n"/>
+      <c r="H196" s="36" t="n"/>
       <c r="I196" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8898,8 +8919,8 @@
         </is>
       </c>
       <c r="F197" s="15" t="n"/>
-      <c r="G197" s="32" t="n"/>
-      <c r="H197" s="32" t="n"/>
+      <c r="G197" s="39" t="n"/>
+      <c r="H197" s="39" t="n"/>
       <c r="I197" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8934,8 +8955,8 @@
         </is>
       </c>
       <c r="F198" s="9" t="n"/>
-      <c r="G198" s="29" t="n"/>
-      <c r="H198" s="29" t="n"/>
+      <c r="G198" s="36" t="n"/>
+      <c r="H198" s="36" t="n"/>
       <c r="I198" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8978,10 +8999,10 @@
           <t>Монтаж пожарного оборудования системы автоматического пожаротушения кладовых В2 с отм. -0.887 до отм. -0.661, подвал в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G199" s="27" t="n">
+      <c r="G199" s="34" t="n">
         <v>45981</v>
       </c>
-      <c r="H199" s="27" t="n">
+      <c r="H199" s="34" t="n">
         <v>45983</v>
       </c>
       <c r="I199" s="4" t="inlineStr">
@@ -9022,10 +9043,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы автоматического пожаротушения кладовых В2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G200" s="27" t="n">
+      <c r="G200" s="34" t="n">
         <v>45989</v>
       </c>
-      <c r="H200" s="27" t="n">
+      <c r="H200" s="34" t="n">
         <v>45989</v>
       </c>
       <c r="I200" s="4" t="inlineStr">
@@ -9062,8 +9083,8 @@
         </is>
       </c>
       <c r="F201" s="7" t="n"/>
-      <c r="G201" s="28" t="n"/>
-      <c r="H201" s="28" t="n"/>
+      <c r="G201" s="35" t="n"/>
+      <c r="H201" s="35" t="n"/>
       <c r="I201" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -9102,10 +9123,10 @@
           <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов систем автоматического пожаротушения кладовых В2 с отм. -0.887 до отм. -0.210, с подвала по 1 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G202" s="27" t="n">
+      <c r="G202" s="34" t="n">
         <v>45996</v>
       </c>
-      <c r="H202" s="27" t="n">
+      <c r="H202" s="34" t="n">
         <v>45996</v>
       </c>
       <c r="I202" s="4" t="inlineStr">
@@ -9150,10 +9171,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G203" s="27" t="n">
+      <c r="G203" s="34" t="n">
         <v>45999</v>
       </c>
-      <c r="H203" s="27" t="n">
+      <c r="H203" s="34" t="n">
         <v>45999</v>
       </c>
       <c r="I203" s="4" t="inlineStr">
@@ -9190,8 +9211,8 @@
         </is>
       </c>
       <c r="F204" s="9" t="n"/>
-      <c r="G204" s="29" t="n"/>
-      <c r="H204" s="29" t="n"/>
+      <c r="G204" s="36" t="n"/>
+      <c r="H204" s="36" t="n"/>
       <c r="I204" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9230,8 +9251,8 @@
         </is>
       </c>
       <c r="F205" s="17" t="n"/>
-      <c r="G205" s="33" t="n"/>
-      <c r="H205" s="33" t="n"/>
+      <c r="G205" s="40" t="n"/>
+      <c r="H205" s="40" t="n"/>
       <c r="I205" s="16" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9270,8 +9291,8 @@
         </is>
       </c>
       <c r="F206" s="15" t="n"/>
-      <c r="G206" s="32" t="n"/>
-      <c r="H206" s="32" t="n"/>
+      <c r="G206" s="39" t="n"/>
+      <c r="H206" s="39" t="n"/>
       <c r="I206" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9306,8 +9327,8 @@
         </is>
       </c>
       <c r="F207" s="9" t="n"/>
-      <c r="G207" s="29" t="n"/>
-      <c r="H207" s="29" t="n"/>
+      <c r="G207" s="36" t="n"/>
+      <c r="H207" s="36" t="n"/>
       <c r="I207" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9350,10 +9371,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов хоз. питьевой насосной станции (сети В1, В1.1, В1.2) (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G208" s="27" t="n">
+      <c r="G208" s="34" t="n">
         <v>45763</v>
       </c>
-      <c r="H208" s="27" t="n">
+      <c r="H208" s="34" t="n">
         <v>45833</v>
       </c>
       <c r="I208" s="4" t="inlineStr">
@@ -9390,8 +9411,8 @@
         </is>
       </c>
       <c r="F209" s="7" t="n"/>
-      <c r="G209" s="28" t="n"/>
-      <c r="H209" s="28" t="n"/>
+      <c r="G209" s="35" t="n"/>
+      <c r="H209" s="35" t="n"/>
       <c r="I209" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -9430,10 +9451,10 @@
           <t>Проведение индивидуального испытания оборудования насосной станции хоз. питьевой водоснабжения (сети В1, В1.1, В1.2) (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G210" s="27" t="n">
+      <c r="G210" s="34" t="n">
         <v>45834</v>
       </c>
-      <c r="H210" s="27" t="n">
+      <c r="H210" s="34" t="n">
         <v>45836</v>
       </c>
       <c r="I210" s="4" t="inlineStr">
@@ -9470,8 +9491,8 @@
         </is>
       </c>
       <c r="F211" s="13" t="n"/>
-      <c r="G211" s="31" t="n"/>
-      <c r="H211" s="31" t="n"/>
+      <c r="G211" s="38" t="n"/>
+      <c r="H211" s="38" t="n"/>
       <c r="I211" s="12" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9506,8 +9527,8 @@
         </is>
       </c>
       <c r="F212" s="9" t="n"/>
-      <c r="G212" s="29" t="n"/>
-      <c r="H212" s="29" t="n"/>
+      <c r="G212" s="36" t="n"/>
+      <c r="H212" s="36" t="n"/>
       <c r="I212" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9542,8 +9563,8 @@
         </is>
       </c>
       <c r="F213" s="9" t="n"/>
-      <c r="G213" s="29" t="n"/>
-      <c r="H213" s="29" t="n"/>
+      <c r="G213" s="36" t="n"/>
+      <c r="H213" s="36" t="n"/>
       <c r="I213" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9578,8 +9599,8 @@
         </is>
       </c>
       <c r="F214" s="9" t="n"/>
-      <c r="G214" s="29" t="n"/>
-      <c r="H214" s="29" t="n"/>
+      <c r="G214" s="36" t="n"/>
+      <c r="H214" s="36" t="n"/>
       <c r="I214" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9622,10 +9643,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов насосной станции пожаротушения (сети В2.1, В2.2, В21) (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G215" s="27" t="n">
+      <c r="G215" s="34" t="n">
         <v>45763</v>
       </c>
-      <c r="H215" s="27" t="n">
+      <c r="H215" s="34" t="n">
         <v>45833</v>
       </c>
       <c r="I215" s="4" t="inlineStr">
@@ -9662,8 +9683,8 @@
         </is>
       </c>
       <c r="F216" s="7" t="n"/>
-      <c r="G216" s="28" t="n"/>
-      <c r="H216" s="28" t="n"/>
+      <c r="G216" s="35" t="n"/>
+      <c r="H216" s="35" t="n"/>
       <c r="I216" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -9702,10 +9723,10 @@
           <t>Проведение индивидуального испытания оборудования насосной станции пожаротушения (сети В2.1, В2.2, В21) (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G217" s="27" t="n">
+      <c r="G217" s="34" t="n">
         <v>45834</v>
       </c>
-      <c r="H217" s="27" t="n">
+      <c r="H217" s="34" t="n">
         <v>45836</v>
       </c>
       <c r="I217" s="4" t="inlineStr">
@@ -9742,8 +9763,8 @@
         </is>
       </c>
       <c r="F218" s="13" t="n"/>
-      <c r="G218" s="31" t="n"/>
-      <c r="H218" s="31" t="n"/>
+      <c r="G218" s="38" t="n"/>
+      <c r="H218" s="38" t="n"/>
       <c r="I218" s="12" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9778,8 +9799,8 @@
         </is>
       </c>
       <c r="F219" s="15" t="n"/>
-      <c r="G219" s="32" t="n"/>
-      <c r="H219" s="32" t="n"/>
+      <c r="G219" s="39" t="n"/>
+      <c r="H219" s="39" t="n"/>
       <c r="I219" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9814,8 +9835,8 @@
         </is>
       </c>
       <c r="F220" s="9" t="n"/>
-      <c r="G220" s="29" t="n"/>
-      <c r="H220" s="29" t="n"/>
+      <c r="G220" s="36" t="n"/>
+      <c r="H220" s="36" t="n"/>
       <c r="I220" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>

--- a/output/spreadsheet/Основная таблица ИБ12 (ВК).xlsx
+++ b/output/spreadsheet/Основная таблица ИБ12 (ВК).xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="База актов" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Даты работ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр (акты)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр (схемы)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр (сертификаты)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="База актов" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Даты работ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Реестр (акты)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Реестр (схемы)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Реестр (сертификаты)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Материалы" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'База актов'!$A$1:$J$220</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Даты работ'!$A$1:$J$220</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Реестр (акты)'!$A$1:$I$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Материалы'!$A$1:$J$141</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -31806,4 +31808,3868 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J141"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Секция</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>№ акта</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Тип акта</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Наименование акта</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Материалы (как в проекте)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Материалы (для акта)</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Сертификаты (по реестру)</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Приложение (если &gt;5 сертификатов)</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Статус проверки</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +4.650, 2 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +7.650, 3 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +10.650, 4 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +13.650, 5 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +16.650, 6 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +19.650, 7 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +22.650, 8 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +25.650, 9 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +28.650, 10 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +31.650, 11 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +34.650, 12 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +37.650, 13 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +40.650, 14 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +43.650, 15 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +46.650, 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж полипропиленовых трубопроводов, гильз для стояков и горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.1,Т3.1,Т4.1 с отм. -0.780 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж этажных распределительных коллекторов систем В1.1, Т3.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 9с-10с/Вс-Гс</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.1, Т3.1 с отм. +0.140 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж водомерных узлов сетей В1.1, Т3.1 на отм. +0.140, 1 этаж в/о 2с-6с/Бс-Дс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гибких подводок и смесителей систем В1.1, Т3.1 с отм. +0.140 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов В1.1,Т3.1,Т4.1 с отм. -0.780 до отм. +46.650, с подвала по 16 этаж в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/1</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Изоляция полипропиленовых трубопроводов систем В1.1,Т3.1,Т4.1 с отм. -0.780 до отм. +48.150, с подвала по 16 этаж в/о 2с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +49.650, 17 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +52.650, 18 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +55.650, 19 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +58.650, 20 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +61.650, 21 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +64.650, 22 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +67.650, 23 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +70.650, 24 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +73.650, 25 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +76.650, 26 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +79.650, 27 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +82.650, 28 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +85.650, 29 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +88.650, 30 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +91.650, 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж полипропиленовых трубопроводов, гильз для стояков и горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.2,Т3.2,Т4.2 с отм. -0.780 до отм. +93.150, с подвала по 31 этаж в/о 9с-11с/Вс-Дс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж этажных распределительных коллекторов систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 9с-10с/Вс-Гс(Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гибких подводок и смесителей систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж устройства внутриквартирного пожаротушения систем В1.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес ( (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода полипропиленовых трубопроводов с отм. -0.780 до отм. +91.650, с подвала по 31 этаж в/о 9с-11с/Вс-Дс систем В1.2,Т3.2,Т4.2 (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/1</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Изоляция полипропиленовых трубопроводов с отм. -0.780 до отм. +93.150, с подвала по 31 этаж в/о 9с-11с/Вс-Дс систем В1.2,Т3.2,Т4.2 (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>К1/1</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж противопожарных манжет, горизонтальной разводки полимерных трубопроводов, стояков и вентиляционных клапанов системы бытовой канализации К1 с отм. -1.390 до отм. +97.350, с подвала по кровлю в/о 1с-11с/Бс-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>К1/1</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>К1/1</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж сантехнического оборудования системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>К1.1/1</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки полимерных трубопроводов, стояков, противопожарных манжет, вентиляционных клапанов системы бытовой канализации встроенных помещений К1.1 с отм. -1.390 до отм. +1.290, с подвала по 1 этаж в/о 2с-8с/Бс-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>К1.1/1</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации встроенных помещений К1.1 на отм. +0.140, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>К1.1/1</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж сантехнического оборудования системы бытовой канализации встроенных помещений К1.1 на отм. +0.140, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>К2/1</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж противопожарных манжет, горизонтальной разводки полимерных трубопроводов, стояков и опусков от дождеприёмных воронок системы внутреннего водостока К2 с отм. -1.151 до отм. +97.350, с подвала по кровлю в/о 2с-11с/Вс-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>К2/1</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Изоляция горизонтальной разводки полимерных трубопроводов стояков и опусков от дождеприёмных воронок системы внутреннего водостока К2 с отм. -1.151 до отм. +97.350, с подвала по кровлю в/о 2с-11с/Вс-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>К13,К13н/1</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз, полимерных трубопроводов горизонтальной разводки и стояков, запорной арматуры и оборудования системы напорной дренажной канализации К13, К13н с отм. -4.350 до отм. +91.650, с подвала по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>К13,К13н/1</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода трубопроводов системы напорной дренажной канализации К13, К13н через ограждающие конструкции с отм. -3.350 до отм. -91.650, с подвала по 31 этаж в/о 1с-11с/Бс-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>В2.1/1</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз, трубопроводов и запорной арматуры системы противопожарного водопровода В2.1 с отм. -2.050 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Ас-Жс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>В2.1/1</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.1 с отм. -3.350 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Ас-Жс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>В2.1/1</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Антикоррозийное покрытие грунтовкой в 1, краской в 2 слоя трубопроводов системы противопожарного водопровода В2.1 с отм. -2.050 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Ас-Жс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>В2.1/1</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов системы противопожарного водопровода В2.1 с отм. -0.970 до отм. +46.650, с подвала по 16 этаж в/о 1с-11с/Ас-Жс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>В2.2/1</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз, стояков, трубопроводов и запорной арматуры системы противопожарного водопровода В2.2 с отм. -0.890 до отм. +97.130, с подвала по тех.чердак в/о 3с-10с/Ас-Дс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>В2.2/1</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.2 с отм. +49.650 до отм. +94.930, с 17 этажа по тех. чердак в/о 3с-10с/Ас-Дс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>В2.2/1</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Антикоррозийное покрытие грунтовкой в 1, краской в 2 слоя трубопроводов системы противопожарного водопровода В2.2 с отм. -0.890 до отм. +97.130, с подвала по тех. чердак в/о 3с-10с/Ас-Дс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>В2.2/1</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов систем противопожарного водопровода В2.2 с отм. -0.890 до отм. +96.978, с подвала по тех. чердак в/о 3с-10с/Бс-Дс (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>В2/1</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз, трубопроводов и запорной арматуры системы автоматического пожаротушения кладовых В2 с отм. -0.862 до отм. -0.289, подвал в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>В2/1</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж пожарного оборудования системы автоматического пожаротушения кладовых В2 с отм. -0.548 до отм. -0.289, подвал в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>В2/1</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Антикоррозийное покрытие трубопроводов грунтовкой в 1, краской в 2 слоя системы автоматического пожаротушения кладовых В2 с отм. -0.862 до отм. -0.422, подвал в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>В2/1</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции системы автоматического пожаротушения кладовых В2 с отм. -0.862 до отм. -0.422, подвал в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж узла ввода системы В1 на отм. -3.350, подвал в/о 1с-2с/Дс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж основного водомерного узла системы В1 с отм. -2.580 до отм. -2.253, подвал в/о 1с-2с/Ес-Жс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +4.650, 2 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +7.650, 3 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +10.650, 4 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +13.650, 5 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +16.650, 6 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +19.650, 7 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +22.650, 8 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +25.650, 9 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +28.650, 10 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +31.650, 11 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +34.650, 12 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +37.650, 13 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +40.650, 14 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +43.650, 15 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +46.650, 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз для стояков, полипропиленовых и стальных трубопроводов, неподвижных опор и запорной арматуры систем В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной с отм. -1.250 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж этажных распределительных коллекторов систем В1.1, Т3.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.1, Т3.1 с отм. -0.210 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж водомерных узлов сетей В1.1, Т3.1 на отм. -0.210, 1 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гибких подводок и смесителей систем В1.1, Т3.1 с отм. -0.210 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной с отм. -1.250 до отм. +46.650, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>В1.1,Т3.1,Т4.1/2</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Изоляция полипропиленовых и стальных трубопроводов систем В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной с отм. -1.250 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +49.650, 17 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +52.650, 18 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +55.650, 19 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +58.650, 20 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +61.650, 21 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +64.650, 22 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +67.650, 23 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +70.650, 24 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +73.650, 25 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +76.650, 26 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +79.650, 27 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +82.650, 28 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +85.650, 29 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +88.650, 30 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +91.650, 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж полипропиленовых трубопроводов, гильз для стояков, горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.2,Т3.2,Т4.2 с отм. -0.947 до отм. +93.150, с подвала по 31 этаж в/о 1с-9с/Вс-Дс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж этажных распределительных коллекторов систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гибких подводок и смесителей систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода полипропиленовых трубопроводов систем В1.2,Т3.2,Т4.2 с отм. -0.947 до отм. +91.650, с подвала по 31 этаж в/о 1с-9с/Вс-Дс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>В1.2,Т3.2,Т4.2/2</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Изоляция полипропиленовых трубопроводов систем В1.2,Т3.2,Т4.2 с отм. -0.947 до отм. +93.150,с подвала по 31 этаж в/о 1с-9с/Вс-Дс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>К1/2</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж горизонтальной разводки полимерных трубопроводов, стояков, противопожарных манжет, вентиляционных клапанов системы бытовой канализации К1 с отм. -1.590 до отм. +97.350, с подвала по кровлю в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>К1/2</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации К1 с отм. +4.650 до отм. +91.650 в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>К1/2</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж сантехнического оборудования системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>К1.1/2</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж противопожарных манжет, горизонтальной разводки полимерных трубопроводов, опусков и вентиляционных клапанов системы бытовой канализации встроенных помещений К1.1 с отм. -1.590 до отм. +1.290, с подвала по 1 этаж в/о 2с-8с/Бс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>К1.1/2</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации встроенных помещений К1.1 на отм. -0.210, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>К1.1/2</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж сантехнического оборудования системы бытовой канализации встроенных помещений К1.1 на отм. -0.210, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>К2/2</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж противопожарных манжет, горизонтальной разводки полимерных трубопроводов, стояков, опусков от дождеприёмных воронок системы внутреннего водостока К2 с отм. -1.321 до отм. +97.350, с подвала по кровлю в/о 2с-11с/Вс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>К2/2</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Изоляция горизонтальной разводки полимерных трубопроводов, опусков от дождеприёмных воронок системы внутреннего водостока К2 с отм. -1.321 до отм. +97.350, с подвала по кровлю в/о 2с-11с/Вс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>К13,К13н,К14н/2</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз, полимерных трубопроводов горизонтальной разводки и стояков, запорной арматуры и оборудования системы напорной дренажной канализации К13, К13н, К14н с отм. -4.350 до отм. +91.650, с подвала по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>К13,К13н,К14н/2</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода трубопроводов системы напорной дренажной канализации К13, К13н, К14н через ограждающие конструкции с отм. -4.350 до отм. -91.650, с подвала по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>В2.1/2</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз, трубопроводов, соединительных головок и запорной арматуры системы противопожарного водопровода В2.1 с отм. -2.050 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>В2.1/2</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.1 с отм. -3.350 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>В2.1/2</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Антикоррозийное покрытие трубопроводов грунтовкой в 1, краской в 2 слоя системы противопожарного водопровода В2.1 с отм. -2.050 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>В2.1/2</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции систем противопожарного водопровода В2.1 с отм. -2.050 до отм. +46.650, с подвала по 16 этаж в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>В2.2/2</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз, трубопроводов, соединительных головок и запорной арматуры системы противопожарного водопровода В2.2 с отм. -1.071 до отм. +97.130, с подвала по тех. чердак в/о 1с-9с/Бс-Дс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>В2.2/2</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.2 с отм. +50.950 до отм. +94.630, с 17 этажа по тех. чердак в/о 1с-9с/Бс-Дс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>В2.2/2</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Антикоррозийное покрытие грунтовкой в 1, краской в 2 слоя трубопроводов системы противопожарного водопровода В2.2 с отм. -1.071 до отм. +97.130, с подвала по тех.чердак в/о 1с-9с/Бс-Дс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>В2.2/2</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции систем противопожарного водопровода В2.2 с отм. -1.071 до отм. +94.930, с подвала по тех. чердак в/о 1с-9с/Бс-Дс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>В2/2</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж гильз, трубопроводов, соединительных головок и запорной арматуры системы автоматического пожаротушения кладовых В2 с отм. -1.216 до отм. -0.210, с подвала по 1 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>В2/2</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж пожарного оборудования системы автоматического пожаротушения кладовых В2 с отм. -0.887 до отм. -0.661, подвал в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>В2/2</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Антикоррозийное покрытие грунтовкой в 1, краской в 2 слоя трубопроводов системы автоматического пожаротушения кладовых В2 с отм. -1.216 до отм. -0.210, с подвала по 1 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>В2/2</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов систем автоматического пожаротушения кладовых В2 с отм. -0.887 до отм. -0.210, с подвала по 1 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>НХП/2</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж и обвязка насосной станции хоз. питьевого водоснабжения (сети В1, В1.1, В1.2) с отм. -3.350 до отм. -0.790, подвал в/о 7с-11с/Ас-Гс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>НХП/2</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Изоляция трубопроводов насосной станции хоз. питьевого водоснабжения (сети В1, В1.1, В1.2) с отм. -3.350 до отм. -0.790, подвал в/о 7с-11с/Ас-Гс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>НСП/2</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Монтаж и обвязка насосной станции пожаротушения (сети В2.1, В2.2, В21) с отм. -3.350 до отм. -0.663, подвал в осях 7с-10с/Ас-Гс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>НСП/2</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Антикоррозийное покрытие трубопроводов грунтовкой в 1, краской в 2 слоя насосной станции пожаротушения (сети В2.1, В2.2, В21) с отм. -3.350 до отм. -0.663, подвал в осях 7с-10с/Ас-Гс (Секция №12.2)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Нужно проверить</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J141"/>
+  <dataValidations count="1">
+    <dataValidation sqref="I2:I141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Нужно проверить,ОК,Исправить"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/spreadsheet/Основная таблица ИБ12 (ВК).xlsx
+++ b/output/spreadsheet/Основная таблица ИБ12 (ВК).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="База актов" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,9 +25,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -50,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +114,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B183"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -137,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -217,27 +221,6 @@
     <xf numFmtId="14" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -258,6 +241,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -722,10 +711,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +7.650, 3 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G2" s="34" t="n">
+      <c r="G2" s="27" t="n">
         <v>45477</v>
       </c>
-      <c r="H2" s="34" t="n">
+      <c r="H2" s="27" t="n">
         <v>45479</v>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -766,10 +755,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +10.650, 4 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G3" s="34" t="n">
+      <c r="G3" s="27" t="n">
         <v>45480</v>
       </c>
-      <c r="H3" s="34" t="n">
+      <c r="H3" s="27" t="n">
         <v>45481</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -810,10 +799,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +13.650, 5 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G4" s="34" t="n">
+      <c r="G4" s="27" t="n">
         <v>45482</v>
       </c>
-      <c r="H4" s="34" t="n">
+      <c r="H4" s="27" t="n">
         <v>45483</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -854,10 +843,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +16.650, 6 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G5" s="34" t="n">
+      <c r="G5" s="27" t="n">
         <v>45484</v>
       </c>
-      <c r="H5" s="34" t="n">
+      <c r="H5" s="27" t="n">
         <v>45488</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -898,10 +887,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +19.650, 7 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="27" t="n">
         <v>45489</v>
       </c>
-      <c r="H6" s="34" t="n">
+      <c r="H6" s="27" t="n">
         <v>45492</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -942,10 +931,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +22.650, 8 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G7" s="34" t="n">
+      <c r="G7" s="27" t="n">
         <v>45518</v>
       </c>
-      <c r="H7" s="34" t="n">
+      <c r="H7" s="27" t="n">
         <v>45522</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -986,10 +975,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +25.650, 9 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G8" s="27" t="n">
         <v>45527</v>
       </c>
-      <c r="H8" s="34" t="n">
+      <c r="H8" s="27" t="n">
         <v>45531</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1030,10 +1019,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +28.650, 10 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="27" t="n">
         <v>45539</v>
       </c>
-      <c r="H9" s="34" t="n">
+      <c r="H9" s="27" t="n">
         <v>45543</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1074,10 +1063,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +31.650, 11 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G10" s="27" t="n">
         <v>45544</v>
       </c>
-      <c r="H10" s="34" t="n">
+      <c r="H10" s="27" t="n">
         <v>45548</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1118,10 +1107,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +34.650, 12 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G11" s="34" t="n">
+      <c r="G11" s="27" t="n">
         <v>45549</v>
       </c>
-      <c r="H11" s="34" t="n">
+      <c r="H11" s="27" t="n">
         <v>45553</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1162,10 +1151,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +37.650, 13 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="27" t="n">
         <v>45554</v>
       </c>
-      <c r="H12" s="34" t="n">
+      <c r="H12" s="27" t="n">
         <v>45587</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1206,10 +1195,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +40.650, 14 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="27" t="n">
         <v>45558</v>
       </c>
-      <c r="H13" s="34" t="n">
+      <c r="H13" s="27" t="n">
         <v>45561</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1250,10 +1239,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +43.650, 15 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="G14" s="27" t="n">
         <v>45562</v>
       </c>
-      <c r="H14" s="34" t="n">
+      <c r="H14" s="27" t="n">
         <v>45565</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1294,10 +1283,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +46.650, 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G15" s="34" t="n">
+      <c r="G15" s="27" t="n">
         <v>45566</v>
       </c>
-      <c r="H15" s="34" t="n">
+      <c r="H15" s="27" t="n">
         <v>45569</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1338,10 +1327,10 @@
           <t>Монтаж полипропиленовых трубопроводов, гильз для стояков и горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.1,Т3.1,Т4.1 с отм. -0.780 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G16" s="34" t="n">
+      <c r="G16" s="27" t="n">
         <v>45570</v>
       </c>
-      <c r="H16" s="34" t="n">
+      <c r="H16" s="27" t="n">
         <v>45573</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1382,10 +1371,10 @@
           <t>Монтаж этажных распределительных коллекторов систем В1.1, Т3.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 9с-10с/Вс-Гс</t>
         </is>
       </c>
-      <c r="G17" s="34" t="n">
+      <c r="G17" s="27" t="n">
         <v>45673</v>
       </c>
-      <c r="H17" s="34" t="n">
+      <c r="H17" s="27" t="n">
         <v>45698</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1426,10 +1415,10 @@
           <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.1, Т3.1 с отм. +0.140 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G18" s="34" t="n">
+      <c r="G18" s="27" t="n">
         <v>45960</v>
       </c>
-      <c r="H18" s="34" t="n">
+      <c r="H18" s="27" t="n">
         <v>45962</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1470,10 +1459,10 @@
           <t>Монтаж водомерных узлов сетей В1.1, Т3.1 на отм. +0.140, 1 этаж в/о 2с-6с/Бс-Дс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G19" s="34" t="n">
+      <c r="G19" s="27" t="n">
         <v>45807</v>
       </c>
-      <c r="H19" s="34" t="n">
+      <c r="H19" s="27" t="n">
         <v>45841</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1514,10 +1503,10 @@
           <t>Монтаж гибких подводок и смесителей систем В1.1, Т3.1 с отм. +0.140 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G20" s="34" t="n">
+      <c r="G20" s="27" t="n">
         <v>45974</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="H20" s="27" t="n">
         <v>45974</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1558,10 +1547,10 @@
           <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="27" t="n">
         <v>45954</v>
       </c>
-      <c r="H21" s="34" t="n">
+      <c r="H21" s="27" t="n">
         <v>45969</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1602,10 +1591,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов систем В1.1,Т3.1,Т4.1 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G22" s="34" t="n">
+      <c r="G22" s="27" t="n">
         <v>45954</v>
       </c>
-      <c r="H22" s="34" t="n">
+      <c r="H22" s="27" t="n">
         <v>45969</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1642,8 +1631,8 @@
         </is>
       </c>
       <c r="F23" s="7" t="n"/>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
+      <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="n"/>
       <c r="I23" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -1682,10 +1671,10 @@
           <t>Изоляция полипропиленовых трубопроводов систем В1.1,Т3.1,Т4.1 с отм. -0.780 до отм. +48.150, с подвала по 16 этаж в/о 2с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G24" s="34" t="n">
+      <c r="G24" s="27" t="n">
         <v>45699</v>
       </c>
-      <c r="H24" s="34" t="n">
+      <c r="H24" s="27" t="n">
         <v>45702</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1726,10 +1715,10 @@
           <t>Проведение промывки трубопроводов системы ХВС (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G25" s="34" t="n">
+      <c r="G25" s="27" t="n">
         <v>45703</v>
       </c>
-      <c r="H25" s="34" t="n">
+      <c r="H25" s="27" t="n">
         <v>45707</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1766,8 +1755,8 @@
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
+      <c r="G26" s="29" t="n"/>
+      <c r="H26" s="29" t="n"/>
       <c r="I26" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1802,8 +1791,8 @@
         </is>
       </c>
       <c r="F27" s="9" t="n"/>
-      <c r="G27" s="36" t="n"/>
-      <c r="H27" s="36" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="29" t="n"/>
       <c r="I27" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1838,8 +1827,8 @@
         </is>
       </c>
       <c r="F28" s="9" t="n"/>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="36" t="n"/>
+      <c r="G28" s="29" t="n"/>
+      <c r="H28" s="29" t="n"/>
       <c r="I28" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1874,8 +1863,8 @@
         </is>
       </c>
       <c r="F29" s="9" t="n"/>
-      <c r="G29" s="36" t="n"/>
-      <c r="H29" s="36" t="n"/>
+      <c r="G29" s="29" t="n"/>
+      <c r="H29" s="29" t="n"/>
       <c r="I29" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1910,8 +1899,8 @@
         </is>
       </c>
       <c r="F30" s="9" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
+      <c r="G30" s="29" t="n"/>
+      <c r="H30" s="29" t="n"/>
       <c r="I30" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -1954,10 +1943,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +52.650, 18 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G31" s="34" t="n">
+      <c r="G31" s="27" t="n">
         <v>45576</v>
       </c>
-      <c r="H31" s="34" t="n">
+      <c r="H31" s="27" t="n">
         <v>45578</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1998,10 +1987,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +55.650, 19 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G32" s="34" t="n">
+      <c r="G32" s="27" t="n">
         <v>45579</v>
       </c>
-      <c r="H32" s="34" t="n">
+      <c r="H32" s="27" t="n">
         <v>45580</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2042,10 +2031,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +58.650, 20 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G33" s="34" t="n">
+      <c r="G33" s="27" t="n">
         <v>45581</v>
       </c>
-      <c r="H33" s="34" t="n">
+      <c r="H33" s="27" t="n">
         <v>45582</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2086,10 +2075,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +61.650, 21 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G34" s="34" t="n">
+      <c r="G34" s="27" t="n">
         <v>45583</v>
       </c>
-      <c r="H34" s="34" t="n">
+      <c r="H34" s="27" t="n">
         <v>45585</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2130,10 +2119,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +64.650, 22 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G35" s="34" t="n">
+      <c r="G35" s="27" t="n">
         <v>45586</v>
       </c>
-      <c r="H35" s="34" t="n">
+      <c r="H35" s="27" t="n">
         <v>45587</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2174,10 +2163,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +67.650, 23 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G36" s="34" t="n">
+      <c r="G36" s="27" t="n">
         <v>45588</v>
       </c>
-      <c r="H36" s="34" t="n">
+      <c r="H36" s="27" t="n">
         <v>45590</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2218,10 +2207,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +70.650, 24 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G37" s="34" t="n">
+      <c r="G37" s="27" t="n">
         <v>45634</v>
       </c>
-      <c r="H37" s="34" t="n">
+      <c r="H37" s="27" t="n">
         <v>45635</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2262,10 +2251,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +73.650, 25 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G38" s="34" t="n">
+      <c r="G38" s="27" t="n">
         <v>45635</v>
       </c>
-      <c r="H38" s="34" t="n">
+      <c r="H38" s="27" t="n">
         <v>45636</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2306,10 +2295,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +76.650, 26 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G39" s="34" t="n">
+      <c r="G39" s="27" t="n">
         <v>45637</v>
       </c>
-      <c r="H39" s="34" t="n">
+      <c r="H39" s="27" t="n">
         <v>45639</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2350,10 +2339,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +79.650, 27 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G40" s="34" t="n">
+      <c r="G40" s="27" t="n">
         <v>45639</v>
       </c>
-      <c r="H40" s="34" t="n">
+      <c r="H40" s="27" t="n">
         <v>45641</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2394,10 +2383,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +82.650, 28 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G41" s="34" t="n">
+      <c r="G41" s="27" t="n">
         <v>45642</v>
       </c>
-      <c r="H41" s="34" t="n">
+      <c r="H41" s="27" t="n">
         <v>45644</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2438,10 +2427,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +85.650, 29 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G42" s="34" t="n">
+      <c r="G42" s="27" t="n">
         <v>45645</v>
       </c>
-      <c r="H42" s="34" t="n">
+      <c r="H42" s="27" t="n">
         <v>45648</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2482,10 +2471,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +88.650, 30 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G43" s="34" t="n">
+      <c r="G43" s="27" t="n">
         <v>45649</v>
       </c>
-      <c r="H43" s="34" t="n">
+      <c r="H43" s="27" t="n">
         <v>45652</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2526,10 +2515,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2на отм. +91.650, 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G44" s="34" t="n">
+      <c r="G44" s="27" t="n">
         <v>45684</v>
       </c>
-      <c r="H44" s="34" t="n">
+      <c r="H44" s="27" t="n">
         <v>45686</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2570,10 +2559,10 @@
           <t>Монтаж полипропиленовых трубопроводов, гильз для стояков и горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.2,Т3.2,Т4.2 с отм. -0.780 до отм. +93.150, с подвала по 31 этаж в/о 9с-11с/Вс-Дс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G45" s="34" t="n">
+      <c r="G45" s="27" t="n">
         <v>45687</v>
       </c>
-      <c r="H45" s="34" t="n">
+      <c r="H45" s="27" t="n">
         <v>45689</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2614,10 +2603,10 @@
           <t>Монтаж этажных распределительных коллекторов систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 9с-10с/Вс-Гс(Секция №12.1)</t>
         </is>
       </c>
-      <c r="G46" s="34" t="n">
+      <c r="G46" s="27" t="n">
         <v>45673</v>
       </c>
-      <c r="H46" s="34" t="n">
+      <c r="H46" s="27" t="n">
         <v>45952</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2658,10 +2647,10 @@
           <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G47" s="34" t="n">
+      <c r="G47" s="27" t="n">
         <v>45963</v>
       </c>
-      <c r="H47" s="34" t="n">
+      <c r="H47" s="27" t="n">
         <v>45965</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2702,10 +2691,10 @@
           <t>Монтаж гибких подводок и смесителей систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G48" s="34" t="n">
+      <c r="G48" s="27" t="n">
         <v>45842</v>
       </c>
-      <c r="H48" s="34" t="n">
+      <c r="H48" s="27" t="n">
         <v>45901</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2746,10 +2735,10 @@
           <t>Монтаж устройства внутриквартирного пожаротушения систем В1.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес ( (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G49" s="34" t="n">
+      <c r="G49" s="27" t="n">
         <v>45970</v>
       </c>
-      <c r="H49" s="34" t="n">
+      <c r="H49" s="27" t="n">
         <v>45982</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2790,10 +2779,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов систем В1.2,Т3.2,Т4.2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G50" s="34" t="n">
+      <c r="G50" s="27" t="n">
         <v>45970</v>
       </c>
-      <c r="H50" s="34" t="n">
+      <c r="H50" s="27" t="n">
         <v>45982</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2830,8 +2819,8 @@
         </is>
       </c>
       <c r="F51" s="7" t="n"/>
-      <c r="G51" s="35" t="n"/>
-      <c r="H51" s="35" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
       <c r="I51" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -2870,10 +2859,10 @@
           <t>Изоляция полипропиленовых трубопроводов с отм. -0.780 до отм. +93.150, с подвала по 31 этаж в/о 9с-11с/Вс-Дс систем В1.2,Т3.2,Т4.2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G52" s="34" t="n">
+      <c r="G52" s="27" t="n">
         <v>45953</v>
       </c>
-      <c r="H52" s="34" t="n">
+      <c r="H52" s="27" t="n">
         <v>45956</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2914,10 +2903,10 @@
           <t>Проведение промывки трубопроводов системы ХВС (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G53" s="34" t="n">
+      <c r="G53" s="27" t="n">
         <v>45957</v>
       </c>
-      <c r="H53" s="34" t="n">
+      <c r="H53" s="27" t="n">
         <v>45961</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2954,8 +2943,8 @@
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
-      <c r="G54" s="36" t="n"/>
-      <c r="H54" s="36" t="n"/>
+      <c r="G54" s="29" t="n"/>
+      <c r="H54" s="29" t="n"/>
       <c r="I54" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -2990,8 +2979,8 @@
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
-      <c r="G55" s="36" t="n"/>
-      <c r="H55" s="36" t="n"/>
+      <c r="G55" s="29" t="n"/>
+      <c r="H55" s="29" t="n"/>
       <c r="I55" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3026,8 +3015,8 @@
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
-      <c r="G56" s="36" t="n"/>
-      <c r="H56" s="36" t="n"/>
+      <c r="G56" s="29" t="n"/>
+      <c r="H56" s="29" t="n"/>
       <c r="I56" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3062,8 +3051,8 @@
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
-      <c r="G57" s="36" t="n"/>
-      <c r="H57" s="36" t="n"/>
+      <c r="G57" s="29" t="n"/>
+      <c r="H57" s="29" t="n"/>
       <c r="I57" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3098,8 +3087,8 @@
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
-      <c r="G58" s="36" t="n"/>
-      <c r="H58" s="36" t="n"/>
+      <c r="G58" s="29" t="n"/>
+      <c r="H58" s="29" t="n"/>
       <c r="I58" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3143,10 +3132,10 @@
           <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G59" s="34" t="n">
+      <c r="G59" s="27" t="n">
         <v>45513</v>
       </c>
-      <c r="H59" s="34" t="n">
+      <c r="H59" s="27" t="n">
         <v>45748</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3187,10 +3176,10 @@
           <t>Монтаж сантехнического оборудования системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G60" s="34" t="n">
+      <c r="G60" s="27" t="n">
         <v>45847</v>
       </c>
-      <c r="H60" s="34" t="n">
+      <c r="H60" s="27" t="n">
         <v>45910</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3231,10 +3220,10 @@
           <t>Проведение испытания систем канализации и водостоков системы бытовой канализации К1 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G61" s="34" t="n">
+      <c r="G61" s="27" t="n">
         <v>45954</v>
       </c>
-      <c r="H61" s="34" t="n">
+      <c r="H61" s="27" t="n">
         <v>45969</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3271,8 +3260,8 @@
         </is>
       </c>
       <c r="F62" s="11" t="n"/>
-      <c r="G62" s="37" t="n"/>
-      <c r="H62" s="37" t="n"/>
+      <c r="G62" s="30" t="n"/>
+      <c r="H62" s="30" t="n"/>
       <c r="I62" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3307,8 +3296,8 @@
         </is>
       </c>
       <c r="F63" s="9" t="n"/>
-      <c r="G63" s="36" t="n"/>
-      <c r="H63" s="36" t="n"/>
+      <c r="G63" s="29" t="n"/>
+      <c r="H63" s="29" t="n"/>
       <c r="I63" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3351,10 +3340,10 @@
           <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации встроенных помещений К1.1 на отм. +0.140, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G64" s="34" t="n">
+      <c r="G64" s="27" t="n">
         <v>45982</v>
       </c>
-      <c r="H64" s="34" t="n">
+      <c r="H64" s="27" t="n">
         <v>45983</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3399,10 +3388,10 @@
           <t>Монтаж сантехнического оборудования системы бытовой канализации встроенных помещений К1.1 на отм. +0.140, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G65" s="34" t="n">
+      <c r="G65" s="27" t="n">
         <v>45984</v>
       </c>
-      <c r="H65" s="34" t="n">
+      <c r="H65" s="27" t="n">
         <v>45984</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3447,10 +3436,10 @@
           <t>Проведение испытания систем канализации и водостоков системы бытовой канализации встроенных помещений К1.1 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G66" s="34" t="n">
+      <c r="G66" s="27" t="n">
         <v>45985</v>
       </c>
-      <c r="H66" s="34" t="n">
+      <c r="H66" s="27" t="n">
         <v>45985</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3491,8 +3480,8 @@
         </is>
       </c>
       <c r="F67" s="11" t="n"/>
-      <c r="G67" s="37" t="n"/>
-      <c r="H67" s="37" t="n"/>
+      <c r="G67" s="30" t="n"/>
+      <c r="H67" s="30" t="n"/>
       <c r="I67" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3527,8 +3516,8 @@
         </is>
       </c>
       <c r="F68" s="9" t="n"/>
-      <c r="G68" s="36" t="n"/>
-      <c r="H68" s="36" t="n"/>
+      <c r="G68" s="29" t="n"/>
+      <c r="H68" s="29" t="n"/>
       <c r="I68" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3572,10 +3561,10 @@
           <t>Проведение испытания систем канализации и водостоков системы внутреннего водостока К2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G69" s="34" t="n">
+      <c r="G69" s="27" t="n">
         <v>45520</v>
       </c>
-      <c r="H69" s="34" t="n">
+      <c r="H69" s="27" t="n">
         <v>45953</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3617,8 +3606,8 @@
         </is>
       </c>
       <c r="F70" s="11" t="n"/>
-      <c r="G70" s="37" t="n"/>
-      <c r="H70" s="37" t="n"/>
+      <c r="G70" s="30" t="n"/>
+      <c r="H70" s="30" t="n"/>
       <c r="I70" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3657,10 +3646,10 @@
           <t>Освидетельствование участков сетей инженерно-технического обеспечения системы внутреннего водостока К2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G71" s="34" t="n">
+      <c r="G71" s="27" t="n">
         <v>45954</v>
       </c>
-      <c r="H71" s="34" t="n">
+      <c r="H71" s="27" t="n">
         <v>45956</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3697,8 +3686,8 @@
         </is>
       </c>
       <c r="F72" s="9" t="n"/>
-      <c r="G72" s="36" t="n"/>
-      <c r="H72" s="36" t="n"/>
+      <c r="G72" s="29" t="n"/>
+      <c r="H72" s="29" t="n"/>
       <c r="I72" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3741,10 +3730,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы напорной дренажной канализации К13, К13н (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G73" s="34" t="n">
+      <c r="G73" s="27" t="n">
         <v>45523</v>
       </c>
-      <c r="H73" s="34" t="n">
+      <c r="H73" s="27" t="n">
         <v>45953</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3781,8 +3770,8 @@
         </is>
       </c>
       <c r="F74" s="7" t="n"/>
-      <c r="G74" s="35" t="n"/>
-      <c r="H74" s="35" t="n"/>
+      <c r="G74" s="28" t="n"/>
+      <c r="H74" s="28" t="n"/>
       <c r="I74" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -3821,10 +3810,10 @@
           <t>Проведение испытания систем канализации и водостоков системы напорной дренажной канализации К13, К13н (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G75" s="34" t="n">
+      <c r="G75" s="27" t="n">
         <v>45954</v>
       </c>
-      <c r="H75" s="34" t="n">
+      <c r="H75" s="27" t="n">
         <v>45954</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3861,8 +3850,8 @@
         </is>
       </c>
       <c r="F76" s="11" t="n"/>
-      <c r="G76" s="37" t="n"/>
-      <c r="H76" s="37" t="n"/>
+      <c r="G76" s="30" t="n"/>
+      <c r="H76" s="30" t="n"/>
       <c r="I76" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3897,8 +3886,8 @@
         </is>
       </c>
       <c r="F77" s="13" t="n"/>
-      <c r="G77" s="38" t="n"/>
-      <c r="H77" s="38" t="n"/>
+      <c r="G77" s="31" t="n"/>
+      <c r="H77" s="31" t="n"/>
       <c r="I77" s="12" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3933,8 +3922,8 @@
         </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="36" t="n"/>
-      <c r="H78" s="36" t="n"/>
+      <c r="G78" s="29" t="n"/>
+      <c r="H78" s="29" t="n"/>
       <c r="I78" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -3977,10 +3966,10 @@
           <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.1 с отм. -3.350 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Ас-Жс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G79" s="34" t="n">
+      <c r="G79" s="27" t="n">
         <v>45478</v>
       </c>
-      <c r="H79" s="34" t="n">
+      <c r="H79" s="27" t="n">
         <v>45917</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4021,10 +4010,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы противопожарного водопровода В2.1 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G80" s="34" t="n">
+      <c r="G80" s="27" t="n">
         <v>45478</v>
       </c>
-      <c r="H80" s="34" t="n">
+      <c r="H80" s="27" t="n">
         <v>45917</v>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4061,8 +4050,8 @@
         </is>
       </c>
       <c r="F81" s="7" t="n"/>
-      <c r="G81" s="35" t="n"/>
-      <c r="H81" s="35" t="n"/>
+      <c r="G81" s="28" t="n"/>
+      <c r="H81" s="28" t="n"/>
       <c r="I81" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -4101,10 +4090,10 @@
           <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов системы противопожарного водопровода В2.1 с отм. -0.970 до отм. +46.650, с подвала по 16 этаж в/о 1с-11с/Ас-Жс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G82" s="34" t="n">
+      <c r="G82" s="27" t="n">
         <v>45918</v>
       </c>
-      <c r="H82" s="34" t="n">
+      <c r="H82" s="27" t="n">
         <v>45919</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4150,10 +4139,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G83" s="34" t="n">
+      <c r="G83" s="27" t="n">
         <v>45920</v>
       </c>
-      <c r="H83" s="34" t="n">
+      <c r="H83" s="27" t="n">
         <v>45921</v>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4190,8 +4179,8 @@
         </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="36" t="n"/>
-      <c r="H84" s="36" t="n"/>
+      <c r="G84" s="29" t="n"/>
+      <c r="H84" s="29" t="n"/>
       <c r="I84" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4226,8 +4215,8 @@
         </is>
       </c>
       <c r="F85" s="15" t="n"/>
-      <c r="G85" s="39" t="n"/>
-      <c r="H85" s="39" t="n"/>
+      <c r="G85" s="32" t="n"/>
+      <c r="H85" s="32" t="n"/>
       <c r="I85" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4262,8 +4251,8 @@
         </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="36" t="n"/>
-      <c r="H86" s="36" t="n"/>
+      <c r="G86" s="29" t="n"/>
+      <c r="H86" s="29" t="n"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4306,10 +4295,10 @@
           <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.2 с отм. +49.650 до отм. +94.930, с 17 этажа по тех. чердак в/о 3с-10с/Ас-Дс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G87" s="34" t="n">
+      <c r="G87" s="27" t="n">
         <v>45478</v>
       </c>
-      <c r="H87" s="34" t="n">
+      <c r="H87" s="27" t="n">
         <v>45876</v>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4350,10 +4339,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы противопожарного водопровода В2.2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G88" s="34" t="n">
+      <c r="G88" s="27" t="n">
         <v>45478</v>
       </c>
-      <c r="H88" s="34" t="n">
+      <c r="H88" s="27" t="n">
         <v>45876</v>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -4390,8 +4379,8 @@
         </is>
       </c>
       <c r="F89" s="7" t="n"/>
-      <c r="G89" s="35" t="n"/>
-      <c r="H89" s="35" t="n"/>
+      <c r="G89" s="28" t="n"/>
+      <c r="H89" s="28" t="n"/>
       <c r="I89" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -4430,10 +4419,10 @@
           <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов систем противопожарного водопровода В2.2 с отм. -0.890 до отм. +96.978, с подвала по тех. чердак в/о 3с-10с/Бс-Дс (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G90" s="34" t="n">
+      <c r="G90" s="27" t="n">
         <v>45877</v>
       </c>
-      <c r="H90" s="34" t="n">
+      <c r="H90" s="27" t="n">
         <v>45878</v>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -4479,10 +4468,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G91" s="34" t="n">
+      <c r="G91" s="27" t="n">
         <v>45879</v>
       </c>
-      <c r="H91" s="34" t="n">
+      <c r="H91" s="27" t="n">
         <v>45880</v>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4519,8 +4508,8 @@
         </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="36" t="n"/>
-      <c r="H92" s="36" t="n"/>
+      <c r="G92" s="29" t="n"/>
+      <c r="H92" s="29" t="n"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4555,8 +4544,8 @@
         </is>
       </c>
       <c r="F93" s="15" t="n"/>
-      <c r="G93" s="39" t="n"/>
-      <c r="H93" s="39" t="n"/>
+      <c r="G93" s="32" t="n"/>
+      <c r="H93" s="32" t="n"/>
       <c r="I93" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4591,8 +4580,8 @@
         </is>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="G94" s="36" t="n"/>
-      <c r="H94" s="36" t="n"/>
+      <c r="G94" s="29" t="n"/>
+      <c r="H94" s="29" t="n"/>
       <c r="I94" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4635,10 +4624,10 @@
           <t>Монтаж пожарного оборудования системы автоматического пожаротушения кладовых В2 с отм. -0.548 до отм. -0.289, подвал в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G95" s="34" t="n">
+      <c r="G95" s="27" t="n">
         <v>45982</v>
       </c>
-      <c r="H95" s="34" t="n">
+      <c r="H95" s="27" t="n">
         <v>45984</v>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -4679,10 +4668,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы автоматического пожаротушения кладовых В2 (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G96" s="34" t="n">
+      <c r="G96" s="27" t="n">
         <v>45988</v>
       </c>
-      <c r="H96" s="34" t="n">
+      <c r="H96" s="27" t="n">
         <v>45988</v>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -4719,8 +4708,8 @@
         </is>
       </c>
       <c r="F97" s="7" t="n"/>
-      <c r="G97" s="35" t="n"/>
-      <c r="H97" s="35" t="n"/>
+      <c r="G97" s="28" t="n"/>
+      <c r="H97" s="28" t="n"/>
       <c r="I97" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -4759,10 +4748,10 @@
           <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции системы автоматического пожаротушения кладовых В2 с отм. -0.862 до отм. -0.422, подвал в/о 1с-11с/Ас-Ис (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G98" s="34" t="n">
+      <c r="G98" s="27" t="n">
         <v>45996</v>
       </c>
-      <c r="H98" s="34" t="n">
+      <c r="H98" s="27" t="n">
         <v>45996</v>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -4807,10 +4796,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.1)</t>
         </is>
       </c>
-      <c r="G99" s="34" t="n">
+      <c r="G99" s="27" t="n">
         <v>45999</v>
       </c>
-      <c r="H99" s="34" t="n">
+      <c r="H99" s="27" t="n">
         <v>45999</v>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -4847,8 +4836,8 @@
         </is>
       </c>
       <c r="F100" s="9" t="n"/>
-      <c r="G100" s="36" t="n"/>
-      <c r="H100" s="36" t="n"/>
+      <c r="G100" s="29" t="n"/>
+      <c r="H100" s="29" t="n"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4883,8 +4872,8 @@
         </is>
       </c>
       <c r="F101" s="17" t="n"/>
-      <c r="G101" s="40" t="n"/>
-      <c r="H101" s="40" t="n"/>
+      <c r="G101" s="33" t="n"/>
+      <c r="H101" s="33" t="n"/>
       <c r="I101" s="16" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4923,8 +4912,8 @@
         </is>
       </c>
       <c r="F102" s="15" t="n"/>
-      <c r="G102" s="39" t="n"/>
-      <c r="H102" s="39" t="n"/>
+      <c r="G102" s="32" t="n"/>
+      <c r="H102" s="32" t="n"/>
       <c r="I102" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -4959,8 +4948,8 @@
         </is>
       </c>
       <c r="F103" s="9" t="n"/>
-      <c r="G103" s="36" t="n"/>
-      <c r="H103" s="36" t="n"/>
+      <c r="G103" s="29" t="n"/>
+      <c r="H103" s="29" t="n"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -5003,10 +4992,10 @@
           <t>Монтаж основного водомерного узла системы В1 с отм. -2.580 до отм. -2.253, подвал в/о 1с-2с/Ес-Жс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G104" s="34" t="n">
+      <c r="G104" s="27" t="n">
         <v>45964</v>
       </c>
-      <c r="H104" s="34" t="n">
+      <c r="H104" s="27" t="n">
         <v>45964</v>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -5047,10 +5036,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +4.650, 2 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G105" s="34" t="n">
+      <c r="G105" s="27" t="n">
         <v>45964</v>
       </c>
-      <c r="H105" s="34" t="n">
+      <c r="H105" s="27" t="n">
         <v>45964</v>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -5091,10 +5080,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +7.650, 3 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G106" s="34" t="n">
+      <c r="G106" s="27" t="n">
         <v>45524</v>
       </c>
-      <c r="H106" s="34" t="n">
+      <c r="H106" s="27" t="n">
         <v>45527</v>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -5139,10 +5128,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +10.650, 4 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G107" s="34" t="n">
+      <c r="G107" s="27" t="n">
         <v>45524</v>
       </c>
-      <c r="H107" s="34" t="n">
+      <c r="H107" s="27" t="n">
         <v>45527</v>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5183,10 +5172,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +13.650, 5 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G108" s="34" t="n">
+      <c r="G108" s="27" t="n">
         <v>45538</v>
       </c>
-      <c r="H108" s="34" t="n">
+      <c r="H108" s="27" t="n">
         <v>45541</v>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -5227,10 +5216,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +16.650, 6 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G109" s="34" t="n">
+      <c r="G109" s="27" t="n">
         <v>45542</v>
       </c>
-      <c r="H109" s="34" t="n">
+      <c r="H109" s="27" t="n">
         <v>45545</v>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -5271,10 +5260,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +19.650, 7 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G110" s="34" t="n">
+      <c r="G110" s="27" t="n">
         <v>45546</v>
       </c>
-      <c r="H110" s="34" t="n">
+      <c r="H110" s="27" t="n">
         <v>45549</v>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -5315,10 +5304,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +22.650, 8 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G111" s="34" t="n">
+      <c r="G111" s="27" t="n">
         <v>45550</v>
       </c>
-      <c r="H111" s="34" t="n">
+      <c r="H111" s="27" t="n">
         <v>45553</v>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -5359,10 +5348,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +25.650, 9 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G112" s="34" t="n">
+      <c r="G112" s="27" t="n">
         <v>45554</v>
       </c>
-      <c r="H112" s="34" t="n">
+      <c r="H112" s="27" t="n">
         <v>45557</v>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -5403,10 +5392,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов 1 из сшитого полиэтилена систем В1.1, Т3.1 на отм. +28.650, 10 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G113" s="34" t="n">
+      <c r="G113" s="27" t="n">
         <v>45567</v>
       </c>
-      <c r="H113" s="34" t="n">
+      <c r="H113" s="27" t="n">
         <v>45570</v>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -5447,10 +5436,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +31.650, 11 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G114" s="34" t="n">
+      <c r="G114" s="27" t="n">
         <v>45571</v>
       </c>
-      <c r="H114" s="34" t="n">
+      <c r="H114" s="27" t="n">
         <v>45574</v>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -5491,10 +5480,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +34.650, 12 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G115" s="34" t="n">
+      <c r="G115" s="27" t="n">
         <v>45575</v>
       </c>
-      <c r="H115" s="34" t="n">
+      <c r="H115" s="27" t="n">
         <v>45577</v>
       </c>
       <c r="I115" s="4" t="inlineStr">
@@ -5535,10 +5524,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +37.650, 13 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G116" s="34" t="n">
+      <c r="G116" s="27" t="n">
         <v>45578</v>
       </c>
-      <c r="H116" s="34" t="n">
+      <c r="H116" s="27" t="n">
         <v>45580</v>
       </c>
       <c r="I116" s="4" t="inlineStr">
@@ -5579,10 +5568,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +40.650, 14 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G117" s="34" t="n">
+      <c r="G117" s="27" t="n">
         <v>45603</v>
       </c>
-      <c r="H117" s="34" t="n">
+      <c r="H117" s="27" t="n">
         <v>45606</v>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -5623,10 +5612,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +43.650, 15 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G118" s="34" t="n">
+      <c r="G118" s="27" t="n">
         <v>45607</v>
       </c>
-      <c r="H118" s="34" t="n">
+      <c r="H118" s="27" t="n">
         <v>45610</v>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -5667,10 +5656,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.1, Т3.1 на отм. +46.650, 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G119" s="34" t="n">
+      <c r="G119" s="27" t="n">
         <v>45611</v>
       </c>
-      <c r="H119" s="34" t="n">
+      <c r="H119" s="27" t="n">
         <v>45614</v>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -5711,10 +5700,10 @@
           <t>Монтаж гильз для стояков, полипропиленовых и стальных трубопроводов, неподвижных опор и запорной арматуры систем В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной с отм. -1.250 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G120" s="34" t="n">
+      <c r="G120" s="27" t="n">
         <v>45634</v>
       </c>
-      <c r="H120" s="34" t="n">
+      <c r="H120" s="27" t="n">
         <v>45637</v>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -5755,10 +5744,10 @@
           <t>Монтаж этажных распределительных коллекторов систем В1.1, Т3.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G121" s="34" t="n">
+      <c r="G121" s="27" t="n">
         <v>45677</v>
       </c>
-      <c r="H121" s="34" t="n">
+      <c r="H121" s="27" t="n">
         <v>45865</v>
       </c>
       <c r="I121" s="4" t="inlineStr">
@@ -5799,10 +5788,10 @@
           <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.1, Т3.1 с отм. -0.210 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G122" s="34" t="n">
+      <c r="G122" s="27" t="n">
         <v>45979</v>
       </c>
-      <c r="H122" s="34" t="n">
+      <c r="H122" s="27" t="n">
         <v>45980</v>
       </c>
       <c r="I122" s="4" t="inlineStr">
@@ -5843,10 +5832,10 @@
           <t>Монтаж водомерных узлов сетей В1.1, Т3.1 на отм. -0.210, 1 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G123" s="34" t="n">
+      <c r="G123" s="27" t="n">
         <v>45812</v>
       </c>
-      <c r="H123" s="34" t="n">
+      <c r="H123" s="27" t="n">
         <v>45851</v>
       </c>
       <c r="I123" s="4" t="inlineStr">
@@ -5887,10 +5876,10 @@
           <t>Монтаж гибких подводок и смесителей систем В1.1, Т3.1 с отм. -0.210 до отм +46.650, с 1 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G124" s="34" t="n">
+      <c r="G124" s="27" t="n">
         <v>45974</v>
       </c>
-      <c r="H124" s="34" t="n">
+      <c r="H124" s="27" t="n">
         <v>45974</v>
       </c>
       <c r="I124" s="4" t="inlineStr">
@@ -5931,10 +5920,10 @@
           <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +4.650 до отм +46.650, со 2 по 16 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G125" s="34" t="n">
+      <c r="G125" s="27" t="n">
         <v>45952</v>
       </c>
-      <c r="H125" s="34" t="n">
+      <c r="H125" s="27" t="n">
         <v>45967</v>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -5975,10 +5964,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов систем В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G126" s="34" t="n">
+      <c r="G126" s="27" t="n">
         <v>45952</v>
       </c>
-      <c r="H126" s="34" t="n">
+      <c r="H126" s="27" t="n">
         <v>45967</v>
       </c>
       <c r="I126" s="4" t="inlineStr">
@@ -6015,8 +6004,8 @@
         </is>
       </c>
       <c r="F127" s="7" t="n"/>
-      <c r="G127" s="35" t="n"/>
-      <c r="H127" s="35" t="n"/>
+      <c r="G127" s="28" t="n"/>
+      <c r="H127" s="28" t="n"/>
       <c r="I127" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -6055,10 +6044,10 @@
           <t>Изоляция полипропиленовых и стальных трубопроводов систем В1.1,Т3.1,Т4.1 и В1 от узла ввода до насосной с отм. -1.250 до отм. +48.150, с подвала по 16 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G128" s="34" t="n">
+      <c r="G128" s="27" t="n">
         <v>45866</v>
       </c>
-      <c r="H128" s="34" t="n">
+      <c r="H128" s="27" t="n">
         <v>45869</v>
       </c>
       <c r="I128" s="4" t="inlineStr">
@@ -6099,10 +6088,10 @@
           <t>Проведение промывки трубопроводов системы ХВС (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G129" s="34" t="n">
+      <c r="G129" s="27" t="n">
         <v>45870</v>
       </c>
-      <c r="H129" s="34" t="n">
+      <c r="H129" s="27" t="n">
         <v>45874</v>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -6139,8 +6128,8 @@
         </is>
       </c>
       <c r="F130" s="9" t="n"/>
-      <c r="G130" s="36" t="n"/>
-      <c r="H130" s="36" t="n"/>
+      <c r="G130" s="29" t="n"/>
+      <c r="H130" s="29" t="n"/>
       <c r="I130" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6175,8 +6164,8 @@
         </is>
       </c>
       <c r="F131" s="9" t="n"/>
-      <c r="G131" s="36" t="n"/>
-      <c r="H131" s="36" t="n"/>
+      <c r="G131" s="29" t="n"/>
+      <c r="H131" s="29" t="n"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6211,8 +6200,8 @@
         </is>
       </c>
       <c r="F132" s="9" t="n"/>
-      <c r="G132" s="36" t="n"/>
-      <c r="H132" s="36" t="n"/>
+      <c r="G132" s="29" t="n"/>
+      <c r="H132" s="29" t="n"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6247,8 +6236,8 @@
         </is>
       </c>
       <c r="F133" s="9" t="n"/>
-      <c r="G133" s="36" t="n"/>
-      <c r="H133" s="36" t="n"/>
+      <c r="G133" s="29" t="n"/>
+      <c r="H133" s="29" t="n"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6283,8 +6272,8 @@
         </is>
       </c>
       <c r="F134" s="9" t="n"/>
-      <c r="G134" s="36" t="n"/>
-      <c r="H134" s="36" t="n"/>
+      <c r="G134" s="29" t="n"/>
+      <c r="H134" s="29" t="n"/>
       <c r="I134" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -6327,10 +6316,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +52.650, 18 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G135" s="34" t="n">
+      <c r="G135" s="27" t="n">
         <v>45643</v>
       </c>
-      <c r="H135" s="34" t="n">
+      <c r="H135" s="27" t="n">
         <v>45645</v>
       </c>
       <c r="I135" s="4" t="inlineStr">
@@ -6371,10 +6360,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +55.650, 19 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G136" s="34" t="n">
+      <c r="G136" s="27" t="n">
         <v>45646</v>
       </c>
-      <c r="H136" s="34" t="n">
+      <c r="H136" s="27" t="n">
         <v>45647</v>
       </c>
       <c r="I136" s="4" t="inlineStr">
@@ -6415,10 +6404,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +58.650, 20 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G137" s="34" t="n">
+      <c r="G137" s="27" t="n">
         <v>45648</v>
       </c>
-      <c r="H137" s="34" t="n">
+      <c r="H137" s="27" t="n">
         <v>45649</v>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -6459,10 +6448,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +61.650, 21 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G138" s="34" t="n">
+      <c r="G138" s="27" t="n">
         <v>45650</v>
       </c>
-      <c r="H138" s="34" t="n">
+      <c r="H138" s="27" t="n">
         <v>45651</v>
       </c>
       <c r="I138" s="4" t="inlineStr">
@@ -6503,10 +6492,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +64.650, 22 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G139" s="34" t="n">
+      <c r="G139" s="27" t="n">
         <v>45652</v>
       </c>
-      <c r="H139" s="34" t="n">
+      <c r="H139" s="27" t="n">
         <v>45654</v>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -6547,10 +6536,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +67.650, 23 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G140" s="34" t="n">
+      <c r="G140" s="27" t="n">
         <v>45655</v>
       </c>
-      <c r="H140" s="34" t="n">
+      <c r="H140" s="27" t="n">
         <v>45657</v>
       </c>
       <c r="I140" s="4" t="inlineStr">
@@ -6591,10 +6580,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +70.650, 24 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G141" s="34" t="n">
+      <c r="G141" s="27" t="n">
         <v>45658</v>
       </c>
-      <c r="H141" s="34" t="n">
+      <c r="H141" s="27" t="n">
         <v>45660</v>
       </c>
       <c r="I141" s="4" t="inlineStr">
@@ -6635,10 +6624,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +73.650, 25 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G142" s="34" t="n">
+      <c r="G142" s="27" t="n">
         <v>45672</v>
       </c>
-      <c r="H142" s="34" t="n">
+      <c r="H142" s="27" t="n">
         <v>45674</v>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -6679,10 +6668,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +76.650, 26 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G143" s="34" t="n">
+      <c r="G143" s="27" t="n">
         <v>45675</v>
       </c>
-      <c r="H143" s="34" t="n">
+      <c r="H143" s="27" t="n">
         <v>45677</v>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -6723,10 +6712,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +79.650, 27 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G144" s="34" t="n">
+      <c r="G144" s="27" t="n">
         <v>45678</v>
       </c>
-      <c r="H144" s="34" t="n">
+      <c r="H144" s="27" t="n">
         <v>45680</v>
       </c>
       <c r="I144" s="4" t="inlineStr">
@@ -6767,10 +6756,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +82.650, 28 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G145" s="34" t="n">
+      <c r="G145" s="27" t="n">
         <v>45681</v>
       </c>
-      <c r="H145" s="34" t="n">
+      <c r="H145" s="27" t="n">
         <v>45683</v>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -6811,10 +6800,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +85.650, 29 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G146" s="34" t="n">
+      <c r="G146" s="27" t="n">
         <v>45684</v>
       </c>
-      <c r="H146" s="34" t="n">
+      <c r="H146" s="27" t="n">
         <v>45686</v>
       </c>
       <c r="I146" s="4" t="inlineStr">
@@ -6855,10 +6844,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +88.650, 30 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G147" s="34" t="n">
+      <c r="G147" s="27" t="n">
         <v>45687</v>
       </c>
-      <c r="H147" s="34" t="n">
+      <c r="H147" s="27" t="n">
         <v>45689</v>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -6899,10 +6888,10 @@
           <t>Монтаж горизонтальной разводки трубопроводов из сшитого полиэтилена систем В1.2, Т3.2 на отм. +91.650, 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G148" s="34" t="n">
+      <c r="G148" s="27" t="n">
         <v>45690</v>
       </c>
-      <c r="H148" s="34" t="n">
+      <c r="H148" s="27" t="n">
         <v>45692</v>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -6943,10 +6932,10 @@
           <t>Монтаж полипропиленовых трубопроводов, гильз для стояков, горизонтальных трубопроводов, неподвижных опор и запорной арматуры систем В1.2,Т3.2,Т4.2 с отм. -0.947 до отм. +93.150, с подвала по 31 этаж в/о 1с-9с/Вс-Дс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G149" s="34" t="n">
+      <c r="G149" s="27" t="n">
         <v>45694</v>
       </c>
-      <c r="H149" s="34" t="n">
+      <c r="H149" s="27" t="n">
         <v>45696</v>
       </c>
       <c r="I149" s="4" t="inlineStr">
@@ -6987,10 +6976,10 @@
           <t>Монтаж этажных распределительных коллекторов систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 8с-9с/Вс-Гс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G150" s="34" t="n">
+      <c r="G150" s="27" t="n">
         <v>45677</v>
       </c>
-      <c r="H150" s="34" t="n">
+      <c r="H150" s="27" t="n">
         <v>45952</v>
       </c>
       <c r="I150" s="4" t="inlineStr">
@@ -7031,10 +7020,10 @@
           <t>Монтаж трубопроводов и запорной арматуры к сантехническому оборудованию систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G151" s="34" t="n">
+      <c r="G151" s="27" t="n">
         <v>45981</v>
       </c>
-      <c r="H151" s="34" t="n">
+      <c r="H151" s="27" t="n">
         <v>45983</v>
       </c>
       <c r="I151" s="4" t="inlineStr">
@@ -7075,10 +7064,10 @@
           <t>Монтаж гибких подводок и смесителей систем В1.2, Т3.2 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G152" s="34" t="n">
+      <c r="G152" s="27" t="n">
         <v>45852</v>
       </c>
-      <c r="H152" s="34" t="n">
+      <c r="H152" s="27" t="n">
         <v>45889</v>
       </c>
       <c r="I152" s="4" t="inlineStr">
@@ -7119,10 +7108,10 @@
           <t>Монтаж устройства внутриквартирного пожаротушения систем В1.1 с отм. +49.650 до отм +91.650, с 17 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G153" s="34" t="n">
+      <c r="G153" s="27" t="n">
         <v>45968</v>
       </c>
-      <c r="H153" s="34" t="n">
+      <c r="H153" s="27" t="n">
         <v>45978</v>
       </c>
       <c r="I153" s="4" t="inlineStr">
@@ -7163,10 +7152,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов систем В1.2,Т3.2,Т4.2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G154" s="34" t="n">
+      <c r="G154" s="27" t="n">
         <v>45968</v>
       </c>
-      <c r="H154" s="34" t="n">
+      <c r="H154" s="27" t="n">
         <v>45978</v>
       </c>
       <c r="I154" s="4" t="inlineStr">
@@ -7203,8 +7192,8 @@
         </is>
       </c>
       <c r="F155" s="7" t="n"/>
-      <c r="G155" s="35" t="n"/>
-      <c r="H155" s="35" t="n"/>
+      <c r="G155" s="28" t="n"/>
+      <c r="H155" s="28" t="n"/>
       <c r="I155" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -7243,10 +7232,10 @@
           <t>Изоляция полипропиленовых трубопроводов систем В1.2,Т3.2,Т4.2 с отм. -0.947 до отм. +93.150,с подвала по 31 этаж в/о 1с-9с/Вс-Дс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G156" s="34" t="n">
+      <c r="G156" s="27" t="n">
         <v>45953</v>
       </c>
-      <c r="H156" s="34" t="n">
+      <c r="H156" s="27" t="n">
         <v>45956</v>
       </c>
       <c r="I156" s="4" t="inlineStr">
@@ -7287,10 +7276,10 @@
           <t>Проведение промывки трубопроводов системы ХВС (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G157" s="34" t="n">
+      <c r="G157" s="27" t="n">
         <v>45957</v>
       </c>
-      <c r="H157" s="34" t="n">
+      <c r="H157" s="27" t="n">
         <v>45961</v>
       </c>
       <c r="I157" s="4" t="inlineStr">
@@ -7327,8 +7316,8 @@
         </is>
       </c>
       <c r="F158" s="9" t="n"/>
-      <c r="G158" s="36" t="n"/>
-      <c r="H158" s="36" t="n"/>
+      <c r="G158" s="29" t="n"/>
+      <c r="H158" s="29" t="n"/>
       <c r="I158" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7363,8 +7352,8 @@
         </is>
       </c>
       <c r="F159" s="9" t="n"/>
-      <c r="G159" s="36" t="n"/>
-      <c r="H159" s="36" t="n"/>
+      <c r="G159" s="29" t="n"/>
+      <c r="H159" s="29" t="n"/>
       <c r="I159" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7399,8 +7388,8 @@
         </is>
       </c>
       <c r="F160" s="9" t="n"/>
-      <c r="G160" s="36" t="n"/>
-      <c r="H160" s="36" t="n"/>
+      <c r="G160" s="29" t="n"/>
+      <c r="H160" s="29" t="n"/>
       <c r="I160" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7435,8 +7424,8 @@
         </is>
       </c>
       <c r="F161" s="9" t="n"/>
-      <c r="G161" s="36" t="n"/>
-      <c r="H161" s="36" t="n"/>
+      <c r="G161" s="29" t="n"/>
+      <c r="H161" s="29" t="n"/>
       <c r="I161" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7471,8 +7460,8 @@
         </is>
       </c>
       <c r="F162" s="9" t="n"/>
-      <c r="G162" s="36" t="n"/>
-      <c r="H162" s="36" t="n"/>
+      <c r="G162" s="29" t="n"/>
+      <c r="H162" s="29" t="n"/>
       <c r="I162" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7515,10 +7504,10 @@
           <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации К1 с отм. +4.650 до отм. +91.650 в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G163" s="34" t="n">
+      <c r="G163" s="27" t="n">
         <v>45516</v>
       </c>
-      <c r="H163" s="34" t="n">
+      <c r="H163" s="27" t="n">
         <v>45748</v>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -7559,10 +7548,10 @@
           <t>Монтаж сантехнического оборудования системы бытовой канализации К1 с отм. +4.650 до отм. +91.650, со 2 по 31 этаж в/о 1с-11с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G164" s="34" t="n">
+      <c r="G164" s="27" t="n">
         <v>45852</v>
       </c>
-      <c r="H164" s="34" t="n">
+      <c r="H164" s="27" t="n">
         <v>45906</v>
       </c>
       <c r="I164" s="4" t="inlineStr">
@@ -7603,10 +7592,10 @@
           <t>Проведение испытания систем канализации и водостоков системы бытовой канализации К1 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G165" s="34" t="n">
+      <c r="G165" s="27" t="n">
         <v>45952</v>
       </c>
-      <c r="H165" s="34" t="n">
+      <c r="H165" s="27" t="n">
         <v>45967</v>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -7643,8 +7632,8 @@
         </is>
       </c>
       <c r="F166" s="11" t="n"/>
-      <c r="G166" s="37" t="n"/>
-      <c r="H166" s="37" t="n"/>
+      <c r="G166" s="30" t="n"/>
+      <c r="H166" s="30" t="n"/>
       <c r="I166" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7679,8 +7668,8 @@
         </is>
       </c>
       <c r="F167" s="9" t="n"/>
-      <c r="G167" s="36" t="n"/>
-      <c r="H167" s="36" t="n"/>
+      <c r="G167" s="29" t="n"/>
+      <c r="H167" s="29" t="n"/>
       <c r="I167" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7723,10 +7712,10 @@
           <t>Монтаж трубопроводов к сантехническому оборудованию системы бытовой канализации встроенных помещений К1.1 на отм. -0.210, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G168" s="34" t="n">
+      <c r="G168" s="27" t="n">
         <v>45985</v>
       </c>
-      <c r="H168" s="34" t="n">
+      <c r="H168" s="27" t="n">
         <v>45986</v>
       </c>
       <c r="I168" s="4" t="inlineStr">
@@ -7771,10 +7760,10 @@
           <t>Монтаж сантехнического оборудования системы бытовой канализации встроенных помещений К1.1 на отм. -0.210, 1 этаж в/о 2с-8с/Бс-Ес (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G169" s="34" t="n">
+      <c r="G169" s="27" t="n">
         <v>45987</v>
       </c>
-      <c r="H169" s="34" t="n">
+      <c r="H169" s="27" t="n">
         <v>45987</v>
       </c>
       <c r="I169" s="4" t="inlineStr">
@@ -7819,10 +7808,10 @@
           <t>Проведение испытания систем канализации и водостоков системы бытовой канализации встроенных помещений К1.1 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G170" s="34" t="n">
+      <c r="G170" s="27" t="n">
         <v>45988</v>
       </c>
-      <c r="H170" s="34" t="n">
+      <c r="H170" s="27" t="n">
         <v>45988</v>
       </c>
       <c r="I170" s="4" t="inlineStr">
@@ -7863,8 +7852,8 @@
         </is>
       </c>
       <c r="F171" s="11" t="n"/>
-      <c r="G171" s="37" t="n"/>
-      <c r="H171" s="37" t="n"/>
+      <c r="G171" s="30" t="n"/>
+      <c r="H171" s="30" t="n"/>
       <c r="I171" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7899,8 +7888,8 @@
         </is>
       </c>
       <c r="F172" s="9" t="n"/>
-      <c r="G172" s="36" t="n"/>
-      <c r="H172" s="36" t="n"/>
+      <c r="G172" s="29" t="n"/>
+      <c r="H172" s="29" t="n"/>
       <c r="I172" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -7944,10 +7933,10 @@
           <t>Проведение испытания систем канализации и водостоков системы внутреннего водостока К2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G173" s="34" t="n">
+      <c r="G173" s="27" t="n">
         <v>45524</v>
       </c>
-      <c r="H173" s="34" t="n">
+      <c r="H173" s="27" t="n">
         <v>45737</v>
       </c>
       <c r="I173" s="4" t="inlineStr">
@@ -7984,8 +7973,8 @@
         </is>
       </c>
       <c r="F174" s="11" t="n"/>
-      <c r="G174" s="37" t="n"/>
-      <c r="H174" s="37" t="n"/>
+      <c r="G174" s="30" t="n"/>
+      <c r="H174" s="30" t="n"/>
       <c r="I174" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8024,10 +8013,10 @@
           <t>Освидетельствование участков сетей инженерно-технического обеспечения системы внутреннего водостока К2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G175" s="34" t="n">
+      <c r="G175" s="27" t="n">
         <v>45911</v>
       </c>
-      <c r="H175" s="34" t="n">
+      <c r="H175" s="27" t="n">
         <v>45913</v>
       </c>
       <c r="I175" s="4" t="inlineStr">
@@ -8064,8 +8053,8 @@
         </is>
       </c>
       <c r="F176" s="9" t="n"/>
-      <c r="G176" s="36" t="n"/>
-      <c r="H176" s="36" t="n"/>
+      <c r="G176" s="29" t="n"/>
+      <c r="H176" s="29" t="n"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8108,10 +8097,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы напорной дренажной канализации К13, К13н, К14н (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G177" s="34" t="n">
+      <c r="G177" s="27" t="n">
         <v>45531</v>
       </c>
-      <c r="H177" s="34" t="n">
+      <c r="H177" s="27" t="n">
         <v>45910</v>
       </c>
       <c r="I177" s="4" t="inlineStr">
@@ -8148,8 +8137,8 @@
         </is>
       </c>
       <c r="F178" s="7" t="n"/>
-      <c r="G178" s="35" t="n"/>
-      <c r="H178" s="35" t="n"/>
+      <c r="G178" s="28" t="n"/>
+      <c r="H178" s="28" t="n"/>
       <c r="I178" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -8188,10 +8177,10 @@
           <t>Проведение испытания систем канализации и водостоков системы напорной дренажной канализации К13, К13н, К14н (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G179" s="34" t="n">
+      <c r="G179" s="27" t="n">
         <v>45911</v>
       </c>
-      <c r="H179" s="34" t="n">
+      <c r="H179" s="27" t="n">
         <v>45911</v>
       </c>
       <c r="I179" s="4" t="inlineStr">
@@ -8228,8 +8217,8 @@
         </is>
       </c>
       <c r="F180" s="11" t="n"/>
-      <c r="G180" s="37" t="n"/>
-      <c r="H180" s="37" t="n"/>
+      <c r="G180" s="30" t="n"/>
+      <c r="H180" s="30" t="n"/>
       <c r="I180" s="10" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8264,8 +8253,8 @@
         </is>
       </c>
       <c r="F181" s="13" t="n"/>
-      <c r="G181" s="38" t="n"/>
-      <c r="H181" s="38" t="n"/>
+      <c r="G181" s="31" t="n"/>
+      <c r="H181" s="31" t="n"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8300,8 +8289,8 @@
         </is>
       </c>
       <c r="F182" s="9" t="n"/>
-      <c r="G182" s="36" t="n"/>
-      <c r="H182" s="36" t="n"/>
+      <c r="G182" s="29" t="n"/>
+      <c r="H182" s="29" t="n"/>
       <c r="I182" s="8" t="inlineStr">
         <is>
           <t>08.12.2025</t>
@@ -8345,10 +8334,10 @@
           <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.1 с отм. -3.350 до отм. +49.150, с подвала по 16 этаж в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G183" s="34" t="n">
+      <c r="G183" s="27" t="n">
         <v>45526</v>
       </c>
-      <c r="H183" s="34" t="n">
+      <c r="H183" s="27" t="n">
         <v>45917</v>
       </c>
       <c r="I183" s="4" t="inlineStr">
@@ -8389,10 +8378,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы противопожарного водопровода В2.1 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G184" s="34" t="n">
+      <c r="G184" s="27" t="n">
         <v>45526</v>
       </c>
-      <c r="H184" s="34" t="n">
+      <c r="H184" s="27" t="n">
         <v>45917</v>
       </c>
       <c r="I184" s="4" t="inlineStr">
@@ -8429,8 +8418,8 @@
         </is>
       </c>
       <c r="F185" s="7" t="n"/>
-      <c r="G185" s="35" t="n"/>
-      <c r="H185" s="35" t="n"/>
+      <c r="G185" s="28" t="n"/>
+      <c r="H185" s="28" t="n"/>
       <c r="I185" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -8469,10 +8458,10 @@
           <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции систем противопожарного водопровода В2.1 с отм. -2.050 до отм. +46.650, с подвала по 16 этаж в/о 1с-11с/Бс-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G186" s="34" t="n">
+      <c r="G186" s="27" t="n">
         <v>45918</v>
       </c>
-      <c r="H186" s="34" t="n">
+      <c r="H186" s="27" t="n">
         <v>45919</v>
       </c>
       <c r="I186" s="4" t="inlineStr">
@@ -8517,10 +8506,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G187" s="34" t="n">
+      <c r="G187" s="27" t="n">
         <v>45920</v>
       </c>
-      <c r="H187" s="34" t="n">
+      <c r="H187" s="27" t="n">
         <v>45921</v>
       </c>
       <c r="I187" s="4" t="inlineStr">
@@ -8557,8 +8546,8 @@
         </is>
       </c>
       <c r="F188" s="9" t="n"/>
-      <c r="G188" s="36" t="n"/>
-      <c r="H188" s="36" t="n"/>
+      <c r="G188" s="29" t="n"/>
+      <c r="H188" s="29" t="n"/>
       <c r="I188" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8593,8 +8582,8 @@
         </is>
       </c>
       <c r="F189" s="15" t="n"/>
-      <c r="G189" s="39" t="n"/>
-      <c r="H189" s="39" t="n"/>
+      <c r="G189" s="32" t="n"/>
+      <c r="H189" s="32" t="n"/>
       <c r="I189" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8629,8 +8618,8 @@
         </is>
       </c>
       <c r="F190" s="9" t="n"/>
-      <c r="G190" s="36" t="n"/>
-      <c r="H190" s="36" t="n"/>
+      <c r="G190" s="29" t="n"/>
+      <c r="H190" s="29" t="n"/>
       <c r="I190" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8673,10 +8662,10 @@
           <t>Монтаж пожарного оборудования системы противопожарного водопровода В2.2 с отм. +50.950 до отм. +94.630, с 17 этажа по тех. чердак в/о 1с-9с/Бс-Дс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G191" s="34" t="n">
+      <c r="G191" s="27" t="n">
         <v>45526</v>
       </c>
-      <c r="H191" s="34" t="n">
+      <c r="H191" s="27" t="n">
         <v>45876</v>
       </c>
       <c r="I191" s="4" t="inlineStr">
@@ -8717,10 +8706,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы противопожарного водопровода В2.2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G192" s="34" t="n">
+      <c r="G192" s="27" t="n">
         <v>45526</v>
       </c>
-      <c r="H192" s="34" t="n">
+      <c r="H192" s="27" t="n">
         <v>45876</v>
       </c>
       <c r="I192" s="4" t="inlineStr">
@@ -8757,8 +8746,8 @@
         </is>
       </c>
       <c r="F193" s="7" t="n"/>
-      <c r="G193" s="35" t="n"/>
-      <c r="H193" s="35" t="n"/>
+      <c r="G193" s="28" t="n"/>
+      <c r="H193" s="28" t="n"/>
       <c r="I193" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -8797,10 +8786,10 @@
           <t>Зачеканка гильз в местах прохода трубопроводов через ограждающие конструкции систем противопожарного водопровода В2.2 с отм. -1.071 до отм. +94.930, с подвала по тех. чердак в/о 1с-9с/Бс-Дс (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G194" s="34" t="n">
+      <c r="G194" s="27" t="n">
         <v>45877</v>
       </c>
-      <c r="H194" s="34" t="n">
+      <c r="H194" s="27" t="n">
         <v>45878</v>
       </c>
       <c r="I194" s="4" t="inlineStr">
@@ -8845,10 +8834,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G195" s="34" t="n">
+      <c r="G195" s="27" t="n">
         <v>45879</v>
       </c>
-      <c r="H195" s="34" t="n">
+      <c r="H195" s="27" t="n">
         <v>45880</v>
       </c>
       <c r="I195" s="4" t="inlineStr">
@@ -8885,8 +8874,8 @@
         </is>
       </c>
       <c r="F196" s="9" t="n"/>
-      <c r="G196" s="36" t="n"/>
-      <c r="H196" s="36" t="n"/>
+      <c r="G196" s="29" t="n"/>
+      <c r="H196" s="29" t="n"/>
       <c r="I196" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8921,8 +8910,8 @@
         </is>
       </c>
       <c r="F197" s="15" t="n"/>
-      <c r="G197" s="39" t="n"/>
-      <c r="H197" s="39" t="n"/>
+      <c r="G197" s="32" t="n"/>
+      <c r="H197" s="32" t="n"/>
       <c r="I197" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -8957,8 +8946,8 @@
         </is>
       </c>
       <c r="F198" s="9" t="n"/>
-      <c r="G198" s="36" t="n"/>
-      <c r="H198" s="36" t="n"/>
+      <c r="G198" s="29" t="n"/>
+      <c r="H198" s="29" t="n"/>
       <c r="I198" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9001,10 +8990,10 @@
           <t>Монтаж пожарного оборудования системы автоматического пожаротушения кладовых В2 с отм. -0.887 до отм. -0.661, подвал в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G199" s="34" t="n">
+      <c r="G199" s="27" t="n">
         <v>45981</v>
       </c>
-      <c r="H199" s="34" t="n">
+      <c r="H199" s="27" t="n">
         <v>45983</v>
       </c>
       <c r="I199" s="4" t="inlineStr">
@@ -9045,10 +9034,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов системы автоматического пожаротушения кладовых В2 (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G200" s="34" t="n">
+      <c r="G200" s="27" t="n">
         <v>45989</v>
       </c>
-      <c r="H200" s="34" t="n">
+      <c r="H200" s="27" t="n">
         <v>45989</v>
       </c>
       <c r="I200" s="4" t="inlineStr">
@@ -9085,8 +9074,8 @@
         </is>
       </c>
       <c r="F201" s="7" t="n"/>
-      <c r="G201" s="35" t="n"/>
-      <c r="H201" s="35" t="n"/>
+      <c r="G201" s="28" t="n"/>
+      <c r="H201" s="28" t="n"/>
       <c r="I201" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -9125,10 +9114,10 @@
           <t>Зачеканка гильз в местах прохода через ограждающие конструкции трубопроводов систем автоматического пожаротушения кладовых В2 с отм. -0.887 до отм. -0.210, с подвала по 1 этаж в/о 1с-10с/Ас-Ис (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G202" s="34" t="n">
+      <c r="G202" s="27" t="n">
         <v>45996</v>
       </c>
-      <c r="H202" s="34" t="n">
+      <c r="H202" s="27" t="n">
         <v>45996</v>
       </c>
       <c r="I202" s="4" t="inlineStr">
@@ -9173,10 +9162,10 @@
           <t>Испытание на водоотдачу внутреннего противопожарного водопровода (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G203" s="34" t="n">
+      <c r="G203" s="27" t="n">
         <v>45999</v>
       </c>
-      <c r="H203" s="34" t="n">
+      <c r="H203" s="27" t="n">
         <v>45999</v>
       </c>
       <c r="I203" s="4" t="inlineStr">
@@ -9213,8 +9202,8 @@
         </is>
       </c>
       <c r="F204" s="9" t="n"/>
-      <c r="G204" s="36" t="n"/>
-      <c r="H204" s="36" t="n"/>
+      <c r="G204" s="29" t="n"/>
+      <c r="H204" s="29" t="n"/>
       <c r="I204" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9253,8 +9242,8 @@
         </is>
       </c>
       <c r="F205" s="17" t="n"/>
-      <c r="G205" s="40" t="n"/>
-      <c r="H205" s="40" t="n"/>
+      <c r="G205" s="33" t="n"/>
+      <c r="H205" s="33" t="n"/>
       <c r="I205" s="16" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9293,8 +9282,8 @@
         </is>
       </c>
       <c r="F206" s="15" t="n"/>
-      <c r="G206" s="39" t="n"/>
-      <c r="H206" s="39" t="n"/>
+      <c r="G206" s="32" t="n"/>
+      <c r="H206" s="32" t="n"/>
       <c r="I206" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9329,8 +9318,8 @@
         </is>
       </c>
       <c r="F207" s="9" t="n"/>
-      <c r="G207" s="36" t="n"/>
-      <c r="H207" s="36" t="n"/>
+      <c r="G207" s="29" t="n"/>
+      <c r="H207" s="29" t="n"/>
       <c r="I207" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9373,10 +9362,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов хоз. питьевой насосной станции (сети В1, В1.1, В1.2) (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G208" s="34" t="n">
+      <c r="G208" s="27" t="n">
         <v>45763</v>
       </c>
-      <c r="H208" s="34" t="n">
+      <c r="H208" s="27" t="n">
         <v>45833</v>
       </c>
       <c r="I208" s="4" t="inlineStr">
@@ -9413,8 +9402,8 @@
         </is>
       </c>
       <c r="F209" s="7" t="n"/>
-      <c r="G209" s="35" t="n"/>
-      <c r="H209" s="35" t="n"/>
+      <c r="G209" s="28" t="n"/>
+      <c r="H209" s="28" t="n"/>
       <c r="I209" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -9453,10 +9442,10 @@
           <t>Проведение индивидуального испытания оборудования насосной станции хоз. питьевой водоснабжения (сети В1, В1.1, В1.2) (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G210" s="34" t="n">
+      <c r="G210" s="27" t="n">
         <v>45834</v>
       </c>
-      <c r="H210" s="34" t="n">
+      <c r="H210" s="27" t="n">
         <v>45836</v>
       </c>
       <c r="I210" s="4" t="inlineStr">
@@ -9493,8 +9482,8 @@
         </is>
       </c>
       <c r="F211" s="13" t="n"/>
-      <c r="G211" s="38" t="n"/>
-      <c r="H211" s="38" t="n"/>
+      <c r="G211" s="31" t="n"/>
+      <c r="H211" s="31" t="n"/>
       <c r="I211" s="12" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9529,8 +9518,8 @@
         </is>
       </c>
       <c r="F212" s="9" t="n"/>
-      <c r="G212" s="36" t="n"/>
-      <c r="H212" s="36" t="n"/>
+      <c r="G212" s="29" t="n"/>
+      <c r="H212" s="29" t="n"/>
       <c r="I212" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9565,8 +9554,8 @@
         </is>
       </c>
       <c r="F213" s="9" t="n"/>
-      <c r="G213" s="36" t="n"/>
-      <c r="H213" s="36" t="n"/>
+      <c r="G213" s="29" t="n"/>
+      <c r="H213" s="29" t="n"/>
       <c r="I213" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9601,8 +9590,8 @@
         </is>
       </c>
       <c r="F214" s="9" t="n"/>
-      <c r="G214" s="36" t="n"/>
-      <c r="H214" s="36" t="n"/>
+      <c r="G214" s="29" t="n"/>
+      <c r="H214" s="29" t="n"/>
       <c r="I214" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9645,10 +9634,10 @@
           <t>Гидростатическое испытание на герметичность трубопроводов насосной станции пожаротушения (сети В2.1, В2.2, В21) (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G215" s="34" t="n">
+      <c r="G215" s="27" t="n">
         <v>45763</v>
       </c>
-      <c r="H215" s="34" t="n">
+      <c r="H215" s="27" t="n">
         <v>45833</v>
       </c>
       <c r="I215" s="4" t="inlineStr">
@@ -9685,8 +9674,8 @@
         </is>
       </c>
       <c r="F216" s="7" t="n"/>
-      <c r="G216" s="35" t="n"/>
-      <c r="H216" s="35" t="n"/>
+      <c r="G216" s="28" t="n"/>
+      <c r="H216" s="28" t="n"/>
       <c r="I216" s="6" t="inlineStr">
         <is>
           <t>04.12.2025</t>
@@ -9725,10 +9714,10 @@
           <t>Проведение индивидуального испытания оборудования насосной станции пожаротушения (сети В2.1, В2.2, В21) (Секция №12.2)</t>
         </is>
       </c>
-      <c r="G217" s="34" t="n">
+      <c r="G217" s="27" t="n">
         <v>45834</v>
       </c>
-      <c r="H217" s="34" t="n">
+      <c r="H217" s="27" t="n">
         <v>45836</v>
       </c>
       <c r="I217" s="4" t="inlineStr">
@@ -9765,8 +9754,8 @@
         </is>
       </c>
       <c r="F218" s="13" t="n"/>
-      <c r="G218" s="38" t="n"/>
-      <c r="H218" s="38" t="n"/>
+      <c r="G218" s="31" t="n"/>
+      <c r="H218" s="31" t="n"/>
       <c r="I218" s="12" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9801,8 +9790,8 @@
         </is>
       </c>
       <c r="F219" s="15" t="n"/>
-      <c r="G219" s="39" t="n"/>
-      <c r="H219" s="39" t="n"/>
+      <c r="G219" s="32" t="n"/>
+      <c r="H219" s="32" t="n"/>
       <c r="I219" s="14" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -9837,8 +9826,8 @@
         </is>
       </c>
       <c r="F220" s="9" t="n"/>
-      <c r="G220" s="36" t="n"/>
-      <c r="H220" s="36" t="n"/>
+      <c r="G220" s="29" t="n"/>
+      <c r="H220" s="29" t="n"/>
       <c r="I220" s="8" t="inlineStr">
         <is>
           <t>09.12.2025</t>
@@ -31066,10 +31055,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="67" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
@@ -31077,729 +31066,812 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Секция</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Наименование документа</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Кем выдан документ, срок действия</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Регистрационный номер документа</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Количество документов, шт.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на трубы ONE PLUS</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>ООО «Трубэксперт» с 08.02.2023г. по 07.02.2026г.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.НВ24.АПТС Н00128/23</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на фитингн для труб ONE PLUS</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>ООО «НИЦ ТЕСТ» с 24.11.2023г. по 23.11.2026г.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.НВ63.Н00424/23</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на гофрированный полиэтилен</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>ООО «Прогресс» с 29.01.2024г. по 28.01.2027г.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.З2001.04ИБФ1.ОСП28.46530</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на трубы стальные электросварные и ВГП</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>ООО «ТехЭкспертКонсалт» с 09.02.2024г. по 08.02.2027г.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>№ЮАЧ1.RU.1406.Н00277</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Информационное письмо на электроды</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>ООО «ЭСАБ» от 20.07.2021г.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>№Б/Н</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на крепежные изделия</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>ООО «Апекс-сертификация» с 27.07.2023г. по 26.07.2026г.</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>№РОСС CN.АЖ49.Н04278</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Декларация о соответствии на стальные фасонные элементы</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>ООО «РУНАК» с 14.09.2021г. по 13.09.2026г.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>ЕАЭС № BY/112 11.01. ТР032 056.01 00694</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Декларация о соответствии на фланцы стальные</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>ООО «Челябинский Фланцевый Завод» с 16.03.2023г. по 09.03.2028г.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА02.В.32845/23</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на хомуты</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>ООО «ВНИИЦИ» с 14.11.2022г. по 13.11.2025г.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.З2001.04ИБФ1. ОСП18.25939</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Декларация о соответствии на краны шаровые</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>ООО «ЛД ПРАЙД» с 08.12.2022г. по 06.12.2027г.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА08.В.88434/22</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Декларация о соответствии на клапаны обратные АДЛ</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>ООО «Торговый Дом АДЛ» с 30.08.2023г. по 26.01.2028г.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА06.В.99162/23</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Декларация о соответствии на трубу нержавеющую</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>ООО «Киберсталь» с 04.08.2020г. по 03.08.2025г.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>ЕАЭС №RU Д-RU.АЯ54.В.03252/20</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на трубу НПВХ</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>«Международный стандарт качества СМК с 05.12.2023г. по 04.12.2026г.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>№RU.МСК.ОС.001.15410</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на трубы и фасонные части для канализации</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>ООО «РУСТЕХЭКСПЕРТИЗА» с 25.10.2022г. по 24.10.2025г.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.З2623.ОС03.00687</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на противопожарные муфта</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>«СЗРЦ СЕРТ» с 25.02.2022г. по 24.02.2027г.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>№ЕАЭС RU C-RU.ПБ74.В.00538/22</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Декларация о соответствии на счетчик Пульсар М</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>ООО «НПП «ТЕПЛОВОДОХРАН» с 19.11.2021г. по 18.11.2026г.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА02.В.74870/21</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Декларация о соответствии на фильтры Aquasfera</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>ООО «Сантехкомплект» с 07.09.2022г. по 05.09.2027г.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-CN.РА06.В.23070/22</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на лакокрасочные материалы</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>ООО «Эксперт-С» с 15.02.2023г. по 14.02.2026г.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.НЕ06.Н02547</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Декларация о соответствии на задвижки KR</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>ООО «Торговый Дом АДЛ» с 18.12.2020г. по 17.12.2025г.</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>ЕАЭС N RU Д-RU.РА01.В.31656/20</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Информационное письмо на сифон</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Федеральное агентство по техническому регулированию и метрологии от 05.10.2017г.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>№16617-ОМ/03</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на унитаз и умывальник</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>ООО «ВНИИЦИ» с 14.12.2021г. по 13.12.2024г.</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.З2001.04ИБФ1.ОСП18.15128</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на поддон</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>ООО «Центр сертификации и экспертизы «Тверьэкс» с 11.03.2022г. по 10.03.2025г.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.АМ05.Н11066</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на канализационный затвор</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>ООО «Лидер» с 17.11.2022г. по 16.11.2025г.</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>№РОСС АТ.НА39.Н01221</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на насосы погружные</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>«ИВАНОВО-СЕРТИФИКАТ» с 13.11.2019г. по 12.11.2024г.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>№ЕАЭС RU C-DE.БЛ08.В.00526/19</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Сертификат соответствия на шнур асбестовый</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>ООО «КАСКАД» с 16.01.2024г. по 15.01.2027г.</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>№РОСС RU.32748.04ЭПЗ0.ОС12.00849</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>общий список</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Информационное письмо на герметик</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>ООО «СЕРКОНС» от 15.12.2015г.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>№01-11/1666</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -31817,21 +31889,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="5" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Секция</t>
@@ -31883,7 +31954,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -31910,7 +31981,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -31937,7 +32008,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -31964,7 +32035,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -31991,7 +32062,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32018,7 +32089,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32045,7 +32116,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32072,7 +32143,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32099,7 +32170,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32126,7 +32197,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32153,7 +32224,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32180,7 +32251,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32207,7 +32278,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32234,7 +32305,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32261,7 +32332,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32288,7 +32359,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="64" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32315,7 +32386,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32342,7 +32413,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32369,7 +32440,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32396,7 +32467,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32423,7 +32494,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="48" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32450,7 +32521,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="48" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32477,7 +32548,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="48" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32504,7 +32575,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32531,7 +32602,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="48" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32558,7 +32629,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32585,7 +32656,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32612,7 +32683,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32639,7 +32710,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="48" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32666,7 +32737,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="48" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32693,7 +32764,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="48" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32720,7 +32791,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="48" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32747,7 +32818,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="48" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32774,7 +32845,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="48" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32801,7 +32872,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="48" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32828,7 +32899,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="48" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32855,7 +32926,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="48" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32882,7 +32953,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="48" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32909,7 +32980,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="64" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32936,7 +33007,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="48" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32963,7 +33034,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="48" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -32990,7 +33061,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="48" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33017,7 +33088,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="48" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33044,7 +33115,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="48" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33071,7 +33142,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="48" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33098,7 +33169,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="64" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33125,7 +33196,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="48" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33152,7 +33223,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33179,7 +33250,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="80" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33206,7 +33277,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33233,7 +33304,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="48" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33260,7 +33331,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="64" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33287,7 +33358,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="64" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33314,7 +33385,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="64" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33341,7 +33412,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="64" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33368,7 +33439,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="48" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33395,7 +33466,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="48" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33422,7 +33493,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="64" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33449,7 +33520,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="64" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33476,7 +33547,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="48" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33503,7 +33574,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="48" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33530,7 +33601,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="64" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33557,7 +33628,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="64" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33584,7 +33655,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33611,7 +33682,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="48" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33638,7 +33709,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="48" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33665,7 +33736,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="48" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
@@ -33692,7 +33763,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="32" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33719,7 +33790,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="32" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33746,7 +33817,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="48" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33773,7 +33844,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="48" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33800,7 +33871,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="48" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33827,7 +33898,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="48" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33854,7 +33925,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="48" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33881,7 +33952,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="48" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33908,7 +33979,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="48" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33935,7 +34006,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="48" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33962,7 +34033,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="48" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -33989,7 +34060,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="48" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34016,7 +34087,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="48" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34043,7 +34114,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="48" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34070,7 +34141,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="48" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34097,7 +34168,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="48" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34124,7 +34195,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="48" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34151,7 +34222,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="64" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34178,7 +34249,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="48" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34205,7 +34276,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="48" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34232,7 +34303,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="32" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34259,7 +34330,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="32" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34286,7 +34357,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="48" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34313,7 +34384,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="64" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34340,7 +34411,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="48" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34367,7 +34438,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="48" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34394,7 +34465,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="48" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34421,7 +34492,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="48" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34448,7 +34519,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="48" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34475,7 +34546,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="48" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34502,7 +34573,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="48" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34529,7 +34600,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="48" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34556,7 +34627,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="48" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34583,7 +34654,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="48" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34610,7 +34681,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="48" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34637,7 +34708,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="48" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34664,7 +34735,7 @@
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="48" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34691,7 +34762,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="48" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34718,7 +34789,7 @@
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="48" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34745,7 +34816,7 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="48" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34772,7 +34843,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="64" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34799,7 +34870,7 @@
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="48" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34826,7 +34897,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="48" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34853,7 +34924,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="48" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34880,7 +34951,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="48" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34907,7 +34978,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="48" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34934,7 +35005,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="48" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34961,7 +35032,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="64" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -34988,7 +35059,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="48" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35015,7 +35086,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="48" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35042,7 +35113,7 @@
         </is>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="80" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35069,7 +35140,7 @@
         </is>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="48" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35096,7 +35167,7 @@
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="48" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35123,7 +35194,7 @@
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="64" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35150,7 +35221,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="64" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35177,7 +35248,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="64" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35204,7 +35275,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="64" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35231,7 +35302,7 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="48" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35258,7 +35329,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="48" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35285,7 +35356,7 @@
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="48" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35312,7 +35383,7 @@
         </is>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="64" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35339,7 +35410,7 @@
         </is>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="64" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35366,7 +35437,7 @@
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="48" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35393,7 +35464,7 @@
         </is>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="64" customHeight="1">
       <c r="A132" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35420,7 +35491,7 @@
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="64" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35447,7 +35518,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="64" customHeight="1">
       <c r="A134" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35474,7 +35545,7 @@
         </is>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="48" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35501,7 +35572,7 @@
         </is>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="64" customHeight="1">
       <c r="A136" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35528,7 +35599,7 @@
         </is>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="64" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35555,7 +35626,7 @@
         </is>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="48" customHeight="1">
       <c r="A138" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35582,7 +35653,7 @@
         </is>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="48" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35609,7 +35680,7 @@
         </is>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="48" customHeight="1">
       <c r="A140" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
@@ -35636,7 +35707,7 @@
         </is>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="48" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
           <t>12.2</t>
